--- a/research/traditional_assets/database/data/tunisia/tunisia_household_products.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_household_products.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1564329010817382</v>
+        <v>0.1562365017301155</v>
       </c>
       <c r="C2">
-        <v>533.8470326650089</v>
+        <v>530.266425694957</v>
       </c>
       <c r="D2">
-        <v>504.0470326650089</v>
+        <v>504.9434256949569</v>
       </c>
       <c r="E2">
-        <v>-177.8</v>
+        <v>-173.323</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.477</v>
       </c>
       <c r="G2">
         <v>29.8</v>
@@ -1445,28 +1445,28 @@
         <v>42.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2251931</v>
       </c>
       <c r="N2">
-        <v>42.9</v>
+        <v>42.6748069</v>
       </c>
       <c r="O2">
-        <v>6.435</v>
+        <v>6.401221035</v>
       </c>
       <c r="P2">
-        <v>36.465</v>
+        <v>36.273585865</v>
       </c>
       <c r="Q2">
-        <v>53.565</v>
+        <v>53.373585865</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1564329010817382</v>
+        <v>0.1573827795253692</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6824263892259379</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>190.5031726105285</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1562365017301155</v>
+        <v>0.1560401023784929</v>
       </c>
       <c r="C3">
-        <v>530.266425694957</v>
+        <v>526.6890126807534</v>
       </c>
       <c r="D3">
-        <v>504.9434256949569</v>
+        <v>505.8430126807534</v>
       </c>
       <c r="E3">
-        <v>-173.323</v>
+        <v>-168.846</v>
       </c>
       <c r="F3">
-        <v>4.477</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="G3">
         <v>29.8</v>
@@ -1527,28 +1527,28 @@
         <v>42.9</v>
       </c>
       <c r="M3">
-        <v>0.2251931</v>
+        <v>0.4503862</v>
       </c>
       <c r="N3">
-        <v>42.6748069</v>
+        <v>42.4496138</v>
       </c>
       <c r="O3">
-        <v>6.401221035</v>
+        <v>6.36744207</v>
       </c>
       <c r="P3">
-        <v>36.273585865</v>
+        <v>36.08217173</v>
       </c>
       <c r="Q3">
-        <v>53.373585865</v>
+        <v>53.18217173</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1573827795253692</v>
+        <v>0.1583520432433602</v>
       </c>
       <c r="T3">
-        <v>0.6824263892259379</v>
+        <v>0.6883542854666466</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>190.5031726105285</v>
+        <v>95.25158630526424</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1560401023784929</v>
+        <v>0.1558437030268703</v>
       </c>
       <c r="C4">
-        <v>526.6890126807534</v>
+        <v>523.1148107235373</v>
       </c>
       <c r="D4">
-        <v>505.8430126807534</v>
+        <v>506.7458107235373</v>
       </c>
       <c r="E4">
-        <v>-168.846</v>
+        <v>-164.369</v>
       </c>
       <c r="F4">
-        <v>8.954000000000001</v>
+        <v>13.431</v>
       </c>
       <c r="G4">
         <v>29.8</v>
@@ -1609,28 +1609,28 @@
         <v>42.9</v>
       </c>
       <c r="M4">
-        <v>0.4503862</v>
+        <v>0.6755792999999999</v>
       </c>
       <c r="N4">
-        <v>42.4496138</v>
+        <v>42.2244207</v>
       </c>
       <c r="O4">
-        <v>6.36744207</v>
+        <v>6.333663104999999</v>
       </c>
       <c r="P4">
-        <v>36.08217173</v>
+        <v>35.890757595</v>
       </c>
       <c r="Q4">
-        <v>53.18217173</v>
+        <v>52.990757595</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1583520432433602</v>
+        <v>0.1593412917802787</v>
       </c>
       <c r="T4">
-        <v>0.6883542854666466</v>
+        <v>0.6944044063721118</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.25158630526424</v>
+        <v>63.50105753684283</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1558437030268703</v>
+        <v>0.1556473036752477</v>
       </c>
       <c r="C5">
-        <v>523.1148107235373</v>
+        <v>519.5438370467486</v>
       </c>
       <c r="D5">
-        <v>506.7458107235373</v>
+        <v>507.6518370467487</v>
       </c>
       <c r="E5">
-        <v>-164.369</v>
+        <v>-159.892</v>
       </c>
       <c r="F5">
-        <v>13.431</v>
+        <v>17.908</v>
       </c>
       <c r="G5">
         <v>29.8</v>
@@ -1691,28 +1691,28 @@
         <v>42.9</v>
       </c>
       <c r="M5">
-        <v>0.6755792999999999</v>
+        <v>0.9007724</v>
       </c>
       <c r="N5">
-        <v>42.2244207</v>
+        <v>41.9992276</v>
       </c>
       <c r="O5">
-        <v>6.333663104999999</v>
+        <v>6.29988414</v>
       </c>
       <c r="P5">
-        <v>35.890757595</v>
+        <v>35.69934345999999</v>
       </c>
       <c r="Q5">
-        <v>52.990757595</v>
+        <v>52.79934346</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1593412917802787</v>
+        <v>0.1603511496617164</v>
       </c>
       <c r="T5">
-        <v>0.6944044063721118</v>
+        <v>0.7005805714631077</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.50105753684283</v>
+        <v>47.62579315263211</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1556473036752477</v>
+        <v>0.1554509043236251</v>
       </c>
       <c r="C6">
-        <v>519.5438370467486</v>
+        <v>515.9761089972266</v>
       </c>
       <c r="D6">
-        <v>507.6518370467487</v>
+        <v>508.5611089972265</v>
       </c>
       <c r="E6">
-        <v>-159.892</v>
+        <v>-155.415</v>
       </c>
       <c r="F6">
-        <v>17.908</v>
+        <v>22.385</v>
       </c>
       <c r="G6">
         <v>29.8</v>
@@ -1773,28 +1773,28 @@
         <v>42.9</v>
       </c>
       <c r="M6">
-        <v>0.9007724</v>
+        <v>1.1259655</v>
       </c>
       <c r="N6">
-        <v>41.9992276</v>
+        <v>41.7740345</v>
       </c>
       <c r="O6">
-        <v>6.29988414</v>
+        <v>6.266105175</v>
       </c>
       <c r="P6">
-        <v>35.69934345999999</v>
+        <v>35.507929325</v>
       </c>
       <c r="Q6">
-        <v>52.79934346</v>
+        <v>52.607929325</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1603511496617164</v>
+        <v>0.1613822677090791</v>
       </c>
       <c r="T6">
-        <v>0.7005805714631077</v>
+        <v>0.7068867610823351</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.62579315263211</v>
+        <v>38.10063452210569</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1554509043236251</v>
+        <v>0.1552545049720025</v>
       </c>
       <c r="C7">
-        <v>515.9761089972266</v>
+        <v>512.4116440463148</v>
       </c>
       <c r="D7">
-        <v>508.5611089972265</v>
+        <v>509.4736440463147</v>
       </c>
       <c r="E7">
-        <v>-155.415</v>
+        <v>-150.938</v>
       </c>
       <c r="F7">
-        <v>22.385</v>
+        <v>26.862</v>
       </c>
       <c r="G7">
         <v>29.8</v>
@@ -1855,28 +1855,28 @@
         <v>42.9</v>
       </c>
       <c r="M7">
-        <v>1.1259655</v>
+        <v>1.3511586</v>
       </c>
       <c r="N7">
-        <v>41.7740345</v>
+        <v>41.5488414</v>
       </c>
       <c r="O7">
-        <v>6.266105175</v>
+        <v>6.23232621</v>
       </c>
       <c r="P7">
-        <v>35.507929325</v>
+        <v>35.31651519</v>
       </c>
       <c r="Q7">
-        <v>52.607929325</v>
+        <v>52.41651519000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1613822677090791</v>
+        <v>0.1624353244383005</v>
       </c>
       <c r="T7">
-        <v>0.7068867610823351</v>
+        <v>0.71332712494878</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.10063452210569</v>
+        <v>31.75052876842141</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1552545049720025</v>
+        <v>0.1550581056203799</v>
       </c>
       <c r="C8">
-        <v>512.4116440463148</v>
+        <v>508.8504597909802</v>
       </c>
       <c r="D8">
-        <v>509.4736440463147</v>
+        <v>510.3894597909802</v>
       </c>
       <c r="E8">
-        <v>-150.938</v>
+        <v>-146.461</v>
       </c>
       <c r="F8">
-        <v>26.862</v>
+        <v>31.339</v>
       </c>
       <c r="G8">
         <v>29.8</v>
@@ -1937,28 +1937,28 @@
         <v>42.9</v>
       </c>
       <c r="M8">
-        <v>1.3511586</v>
+        <v>1.5763517</v>
       </c>
       <c r="N8">
-        <v>41.5488414</v>
+        <v>41.3236483</v>
       </c>
       <c r="O8">
-        <v>6.23232621</v>
+        <v>6.198547245</v>
       </c>
       <c r="P8">
-        <v>35.31651519</v>
+        <v>35.125101055</v>
       </c>
       <c r="Q8">
-        <v>52.41651519000001</v>
+        <v>52.225101055</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1624353244383005</v>
+        <v>0.1635110275487956</v>
       </c>
       <c r="T8">
-        <v>0.71332712494878</v>
+        <v>0.7199059912639658</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.75052876842142</v>
+        <v>27.21473894436122</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1550581056203799</v>
+        <v>0.1548617062687573</v>
       </c>
       <c r="C9">
-        <v>508.8504597909803</v>
+        <v>505.2925739549468</v>
       </c>
       <c r="D9">
-        <v>510.3894597909804</v>
+        <v>511.3085739549468</v>
       </c>
       <c r="E9">
-        <v>-146.461</v>
+        <v>-141.984</v>
       </c>
       <c r="F9">
-        <v>31.339</v>
+        <v>35.816</v>
       </c>
       <c r="G9">
         <v>29.8</v>
@@ -2019,28 +2019,28 @@
         <v>42.9</v>
       </c>
       <c r="M9">
-        <v>1.5763517</v>
+        <v>1.8015448</v>
       </c>
       <c r="N9">
-        <v>41.3236483</v>
+        <v>41.0984552</v>
       </c>
       <c r="O9">
-        <v>6.198547245</v>
+        <v>6.16476828</v>
       </c>
       <c r="P9">
-        <v>35.125101055</v>
+        <v>34.93368692</v>
       </c>
       <c r="Q9">
-        <v>52.225101055</v>
+        <v>52.03368692</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1635110275487956</v>
+        <v>0.1646101155095188</v>
       </c>
       <c r="T9">
-        <v>0.7199059912639658</v>
+        <v>0.7266278764120904</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.21473894436121</v>
+        <v>23.81289657631606</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1548617062687573</v>
+        <v>0.1546653069171346</v>
       </c>
       <c r="C10">
-        <v>505.2925739549468</v>
+        <v>501.7380043898353</v>
       </c>
       <c r="D10">
-        <v>511.3085739549468</v>
+        <v>512.2310043898353</v>
       </c>
       <c r="E10">
-        <v>-141.984</v>
+        <v>-137.507</v>
       </c>
       <c r="F10">
-        <v>35.816</v>
+        <v>40.293</v>
       </c>
       <c r="G10">
         <v>29.8</v>
@@ -2101,28 +2101,28 @@
         <v>42.9</v>
       </c>
       <c r="M10">
-        <v>1.8015448</v>
+        <v>2.0267379</v>
       </c>
       <c r="N10">
-        <v>41.0984552</v>
+        <v>40.8732621</v>
       </c>
       <c r="O10">
-        <v>6.16476828</v>
+        <v>6.130989315</v>
       </c>
       <c r="P10">
-        <v>34.93368692</v>
+        <v>34.742272785</v>
       </c>
       <c r="Q10">
-        <v>52.03368692</v>
+        <v>51.842272785</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1646101155095188</v>
+        <v>0.1657333592495985</v>
       </c>
       <c r="T10">
-        <v>0.7266278764120904</v>
+        <v>0.7334974952997341</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.81289657631606</v>
+        <v>21.16701917894761</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1546653069171346</v>
+        <v>0.1544689075655121</v>
       </c>
       <c r="C11">
-        <v>501.7380043898353</v>
+        <v>498.186769076321</v>
       </c>
       <c r="D11">
-        <v>512.2310043898353</v>
+        <v>513.156769076321</v>
       </c>
       <c r="E11">
-        <v>-137.507</v>
+        <v>-133.03</v>
       </c>
       <c r="F11">
-        <v>40.293</v>
+        <v>44.77</v>
       </c>
       <c r="G11">
         <v>29.8</v>
@@ -2183,28 +2183,28 @@
         <v>42.9</v>
       </c>
       <c r="M11">
-        <v>2.0267379</v>
+        <v>2.251931</v>
       </c>
       <c r="N11">
-        <v>40.8732621</v>
+        <v>40.648069</v>
       </c>
       <c r="O11">
-        <v>6.130989315</v>
+        <v>6.09721035</v>
       </c>
       <c r="P11">
-        <v>34.742272785</v>
+        <v>34.55085865</v>
       </c>
       <c r="Q11">
-        <v>51.842272785</v>
+        <v>51.65085865</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1657333592495985</v>
+        <v>0.1668815639616801</v>
       </c>
       <c r="T11">
-        <v>0.7334974952997341</v>
+        <v>0.7405197723848812</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.16701917894761</v>
+        <v>19.05031726105285</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1544689075655121</v>
+        <v>0.1542725082138895</v>
       </c>
       <c r="C12">
-        <v>498.186769076321</v>
+        <v>494.6388861253029</v>
       </c>
       <c r="D12">
-        <v>513.156769076321</v>
+        <v>514.085886125303</v>
       </c>
       <c r="E12">
-        <v>-133.03</v>
+        <v>-128.553</v>
       </c>
       <c r="F12">
-        <v>44.77</v>
+        <v>49.247</v>
       </c>
       <c r="G12">
         <v>29.8</v>
@@ -2265,28 +2265,28 @@
         <v>42.9</v>
       </c>
       <c r="M12">
-        <v>2.251931</v>
+        <v>2.4771241</v>
       </c>
       <c r="N12">
-        <v>40.648069</v>
+        <v>40.4228759</v>
       </c>
       <c r="O12">
-        <v>6.09721035</v>
+        <v>6.063431385</v>
       </c>
       <c r="P12">
-        <v>34.55085865</v>
+        <v>34.359444515</v>
       </c>
       <c r="Q12">
-        <v>51.65085865</v>
+        <v>51.459444515</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1668815639616801</v>
+        <v>0.1680555710268421</v>
       </c>
       <c r="T12">
-        <v>0.7405197723848812</v>
+        <v>0.7476998534494697</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.05031726105285</v>
+        <v>17.31847023732077</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1542725082138895</v>
+        <v>0.1540761088622669</v>
       </c>
       <c r="C13">
-        <v>494.6388861253029</v>
+        <v>491.0943737790823</v>
       </c>
       <c r="D13">
-        <v>514.085886125303</v>
+        <v>515.0183737790824</v>
       </c>
       <c r="E13">
-        <v>-128.553</v>
+        <v>-124.076</v>
       </c>
       <c r="F13">
-        <v>49.247</v>
+        <v>53.724</v>
       </c>
       <c r="G13">
         <v>29.8</v>
@@ -2347,28 +2347,28 @@
         <v>42.9</v>
       </c>
       <c r="M13">
-        <v>2.4771241</v>
+        <v>2.7023172</v>
       </c>
       <c r="N13">
-        <v>40.4228759</v>
+        <v>40.1976828</v>
       </c>
       <c r="O13">
-        <v>6.063431385</v>
+        <v>6.029652419999999</v>
       </c>
       <c r="P13">
-        <v>34.359444515</v>
+        <v>34.16803038</v>
       </c>
       <c r="Q13">
-        <v>51.459444515</v>
+        <v>51.26803038</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1680555710268421</v>
+        <v>0.1692562600707578</v>
       </c>
       <c r="T13">
-        <v>0.7476998534494697</v>
+        <v>0.7550431181746169</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.31847023732077</v>
+        <v>15.87526438421071</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1540761088622669</v>
+        <v>0.1538797095106443</v>
       </c>
       <c r="C14">
-        <v>491.0943737790823</v>
+        <v>487.5532504125588</v>
       </c>
       <c r="D14">
-        <v>515.0183737790824</v>
+        <v>515.9542504125588</v>
       </c>
       <c r="E14">
-        <v>-124.076</v>
+        <v>-119.599</v>
       </c>
       <c r="F14">
-        <v>53.724</v>
+        <v>58.201</v>
       </c>
       <c r="G14">
         <v>29.8</v>
@@ -2429,28 +2429,28 @@
         <v>42.9</v>
       </c>
       <c r="M14">
-        <v>2.7023172</v>
+        <v>2.9275103</v>
       </c>
       <c r="N14">
-        <v>40.1976828</v>
+        <v>39.9724897</v>
       </c>
       <c r="O14">
-        <v>6.029652419999999</v>
+        <v>5.995873454999999</v>
       </c>
       <c r="P14">
-        <v>34.16803038</v>
+        <v>33.976616245</v>
       </c>
       <c r="Q14">
-        <v>51.26803038</v>
+        <v>51.076616245</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1692562600707578</v>
+        <v>0.1704845511616601</v>
       </c>
       <c r="T14">
-        <v>0.7550431181746169</v>
+        <v>0.7625551935831009</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.87526438421071</v>
+        <v>14.65409020080988</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1538797095106443</v>
+        <v>0.1536833101590216</v>
       </c>
       <c r="C15">
-        <v>487.5532504125588</v>
+        <v>484.0155345344364</v>
       </c>
       <c r="D15">
-        <v>515.9542504125588</v>
+        <v>516.8935345344364</v>
       </c>
       <c r="E15">
-        <v>-119.599</v>
+        <v>-115.122</v>
       </c>
       <c r="F15">
-        <v>58.201</v>
+        <v>62.678</v>
       </c>
       <c r="G15">
         <v>29.8</v>
@@ -2511,28 +2511,28 @@
         <v>42.9</v>
       </c>
       <c r="M15">
-        <v>2.9275103</v>
+        <v>3.1527034</v>
       </c>
       <c r="N15">
-        <v>39.9724897</v>
+        <v>39.7472966</v>
       </c>
       <c r="O15">
-        <v>5.995873454999999</v>
+        <v>5.962094489999999</v>
       </c>
       <c r="P15">
-        <v>33.976616245</v>
+        <v>33.78520211</v>
       </c>
       <c r="Q15">
-        <v>51.076616245</v>
+        <v>50.88520211</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1704845511616601</v>
+        <v>0.1717414071616531</v>
       </c>
       <c r="T15">
-        <v>0.7625551935831009</v>
+        <v>0.7702419684196892</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.65409020080988</v>
+        <v>13.6073694721806</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1536833101590216</v>
+        <v>0.153678160807399</v>
       </c>
       <c r="C16">
-        <v>484.0155345344364</v>
+        <v>479.5632074296809</v>
       </c>
       <c r="D16">
-        <v>516.8935345344364</v>
+        <v>516.9182074296809</v>
       </c>
       <c r="E16">
-        <v>-115.122</v>
+        <v>-110.645</v>
       </c>
       <c r="F16">
-        <v>62.678</v>
+        <v>67.155</v>
       </c>
       <c r="G16">
         <v>29.8</v>
@@ -2593,45 +2593,45 @@
         <v>42.9</v>
       </c>
       <c r="M16">
-        <v>3.1527034</v>
+        <v>3.478629</v>
       </c>
       <c r="N16">
-        <v>39.7472966</v>
+        <v>39.421371</v>
       </c>
       <c r="O16">
-        <v>5.962094489999999</v>
+        <v>5.91320565</v>
       </c>
       <c r="P16">
-        <v>33.78520211</v>
+        <v>33.50816535</v>
       </c>
       <c r="Q16">
-        <v>50.88520211</v>
+        <v>50.60816535</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1717414071616531</v>
+        <v>0.1730278362439989</v>
       </c>
       <c r="T16">
-        <v>0.7702419684196892</v>
+        <v>0.7781096085465501</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.6073694721806</v>
+        <v>12.3324447648772</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.153678160807399</v>
+        <v>0.1534945114557764</v>
       </c>
       <c r="C17">
-        <v>479.5632074296809</v>
+        <v>475.9676979750497</v>
       </c>
       <c r="D17">
-        <v>516.9182074296809</v>
+        <v>517.7996979750498</v>
       </c>
       <c r="E17">
-        <v>-110.645</v>
+        <v>-106.168</v>
       </c>
       <c r="F17">
-        <v>67.155</v>
+        <v>71.63200000000001</v>
       </c>
       <c r="G17">
         <v>29.8</v>
@@ -2675,28 +2675,28 @@
         <v>42.9</v>
       </c>
       <c r="M17">
-        <v>3.478629</v>
+        <v>3.7105376</v>
       </c>
       <c r="N17">
-        <v>39.421371</v>
+        <v>39.1894624</v>
       </c>
       <c r="O17">
-        <v>5.91320565</v>
+        <v>5.87841936</v>
       </c>
       <c r="P17">
-        <v>33.50816535</v>
+        <v>33.31104303999999</v>
       </c>
       <c r="Q17">
-        <v>50.60816535</v>
+        <v>50.41104304</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1730278362439989</v>
+        <v>0.17434489459021</v>
       </c>
       <c r="T17">
-        <v>0.7781096085465501</v>
+        <v>0.7861645734383365</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.3324447648772</v>
+        <v>11.56166696707237</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1534945114557764</v>
+        <v>0.1533108621041538</v>
       </c>
       <c r="C18">
-        <v>475.9676979750497</v>
+        <v>472.3752000331893</v>
       </c>
       <c r="D18">
-        <v>517.7996979750498</v>
+        <v>518.6842000331894</v>
       </c>
       <c r="E18">
-        <v>-106.168</v>
+        <v>-101.691</v>
       </c>
       <c r="F18">
-        <v>71.63200000000001</v>
+        <v>76.10900000000001</v>
       </c>
       <c r="G18">
         <v>29.8</v>
@@ -2757,28 +2757,28 @@
         <v>42.9</v>
       </c>
       <c r="M18">
-        <v>3.7105376</v>
+        <v>3.9424462</v>
       </c>
       <c r="N18">
-        <v>39.1894624</v>
+        <v>38.9575538</v>
       </c>
       <c r="O18">
-        <v>5.87841936</v>
+        <v>5.84363307</v>
       </c>
       <c r="P18">
-        <v>33.31104303999999</v>
+        <v>33.11392073</v>
       </c>
       <c r="Q18">
-        <v>50.41104304</v>
+        <v>50.21392073</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.17434489459021</v>
+        <v>0.175693689282113</v>
       </c>
       <c r="T18">
-        <v>0.7861645734383365</v>
+        <v>0.7944136338696838</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.56166696707237</v>
+        <v>10.88156891018576</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1533108621041538</v>
+        <v>0.1531272127525312</v>
       </c>
       <c r="C19">
-        <v>472.3752000331893</v>
+        <v>468.7857290632467</v>
       </c>
       <c r="D19">
-        <v>518.6842000331894</v>
+        <v>519.5717290632467</v>
       </c>
       <c r="E19">
-        <v>-101.691</v>
+        <v>-97.214</v>
       </c>
       <c r="F19">
-        <v>76.10900000000001</v>
+        <v>80.58600000000001</v>
       </c>
       <c r="G19">
         <v>29.8</v>
@@ -2839,28 +2839,28 @@
         <v>42.9</v>
       </c>
       <c r="M19">
-        <v>3.9424462</v>
+        <v>4.174354800000001</v>
       </c>
       <c r="N19">
-        <v>38.9575538</v>
+        <v>38.7256452</v>
       </c>
       <c r="O19">
-        <v>5.84363307</v>
+        <v>5.808846779999999</v>
       </c>
       <c r="P19">
-        <v>33.11392073</v>
+        <v>32.91679842</v>
       </c>
       <c r="Q19">
-        <v>50.21392073</v>
+        <v>50.01679842</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.175693689282113</v>
+        <v>0.1770753814055259</v>
       </c>
       <c r="T19">
-        <v>0.7944136338696838</v>
+        <v>0.8028638908969176</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.88156891018576</v>
+        <v>10.27703730406433</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1531272127525312</v>
+        <v>0.1532181134009086</v>
       </c>
       <c r="C20">
-        <v>468.7857290632464</v>
+        <v>463.869050823189</v>
       </c>
       <c r="D20">
-        <v>519.5717290632465</v>
+        <v>519.132050823189</v>
       </c>
       <c r="E20">
-        <v>-97.21400000000001</v>
+        <v>-92.73700000000001</v>
       </c>
       <c r="F20">
-        <v>80.586</v>
+        <v>85.063</v>
       </c>
       <c r="G20">
         <v>29.8</v>
@@ -2921,45 +2921,45 @@
         <v>42.9</v>
       </c>
       <c r="M20">
-        <v>4.1743548</v>
+        <v>4.5508705</v>
       </c>
       <c r="N20">
-        <v>38.7256452</v>
+        <v>38.3491295</v>
       </c>
       <c r="O20">
-        <v>5.808846780000001</v>
+        <v>5.752369424999999</v>
       </c>
       <c r="P20">
-        <v>32.91679842</v>
+        <v>32.596760075</v>
       </c>
       <c r="Q20">
-        <v>50.01679842</v>
+        <v>49.696760075</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1770753814055259</v>
+        <v>0.1784911893838378</v>
       </c>
       <c r="T20">
-        <v>0.8028638908969176</v>
+        <v>0.8115227962458116</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.27703730406433</v>
+        <v>9.426767911765451</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1532181134009086</v>
+        <v>0.153048914049286</v>
       </c>
       <c r="C21">
-        <v>463.869050823189</v>
+        <v>460.2110503178173</v>
       </c>
       <c r="D21">
-        <v>519.132050823189</v>
+        <v>519.9510503178174</v>
       </c>
       <c r="E21">
-        <v>-92.73700000000001</v>
+        <v>-88.26000000000001</v>
       </c>
       <c r="F21">
-        <v>85.063</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="G21">
         <v>29.8</v>
@@ -3003,28 +3003,28 @@
         <v>42.9</v>
       </c>
       <c r="M21">
-        <v>4.5508705</v>
+        <v>4.79039</v>
       </c>
       <c r="N21">
-        <v>38.3491295</v>
+        <v>38.10961</v>
       </c>
       <c r="O21">
-        <v>5.752369424999999</v>
+        <v>5.716441499999999</v>
       </c>
       <c r="P21">
-        <v>32.596760075</v>
+        <v>32.39316849999999</v>
       </c>
       <c r="Q21">
-        <v>49.696760075</v>
+        <v>49.4931685</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1784911893838378</v>
+        <v>0.1799423925616075</v>
       </c>
       <c r="T21">
-        <v>0.8115227962458116</v>
+        <v>0.8203981742284279</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.426767911765451</v>
+        <v>8.955429516177178</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.153048914049286</v>
+        <v>0.1528797146976634</v>
       </c>
       <c r="C22">
-        <v>460.2110503178173</v>
+        <v>456.5556380558651</v>
       </c>
       <c r="D22">
-        <v>519.9510503178174</v>
+        <v>520.7726380558652</v>
       </c>
       <c r="E22">
-        <v>-88.26000000000001</v>
+        <v>-83.783</v>
       </c>
       <c r="F22">
-        <v>89.54000000000001</v>
+        <v>94.01700000000001</v>
       </c>
       <c r="G22">
         <v>29.8</v>
@@ -3085,28 +3085,28 @@
         <v>42.9</v>
       </c>
       <c r="M22">
-        <v>4.79039</v>
+        <v>5.0299095</v>
       </c>
       <c r="N22">
-        <v>38.10961</v>
+        <v>37.8700905</v>
       </c>
       <c r="O22">
-        <v>5.716441499999999</v>
+        <v>5.680513574999999</v>
       </c>
       <c r="P22">
-        <v>32.39316849999999</v>
+        <v>32.189576925</v>
       </c>
       <c r="Q22">
-        <v>49.4931685</v>
+        <v>49.289576925</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1799423925616075</v>
+        <v>0.1814303350603334</v>
       </c>
       <c r="T22">
-        <v>0.8203981742284279</v>
+        <v>0.8294982453245282</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.955429516177178</v>
+        <v>8.528980491597313</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1528797146976634</v>
+        <v>0.1527105153460408</v>
       </c>
       <c r="C23">
-        <v>456.5556380558651</v>
+        <v>452.9028263259959</v>
       </c>
       <c r="D23">
-        <v>520.7726380558652</v>
+        <v>521.5968263259959</v>
       </c>
       <c r="E23">
-        <v>-83.78300000000002</v>
+        <v>-79.30600000000001</v>
       </c>
       <c r="F23">
-        <v>94.017</v>
+        <v>98.494</v>
       </c>
       <c r="G23">
         <v>29.8</v>
@@ -3167,28 +3167,28 @@
         <v>42.9</v>
       </c>
       <c r="M23">
-        <v>5.0299095</v>
+        <v>5.269429</v>
       </c>
       <c r="N23">
-        <v>37.8700905</v>
+        <v>37.630571</v>
       </c>
       <c r="O23">
-        <v>5.680513574999999</v>
+        <v>5.644585649999999</v>
       </c>
       <c r="P23">
-        <v>32.189576925</v>
+        <v>31.98598535</v>
       </c>
       <c r="Q23">
-        <v>49.289576925</v>
+        <v>49.08598535</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1814303350603334</v>
+        <v>0.1829564299308215</v>
       </c>
       <c r="T23">
-        <v>0.8294982453245281</v>
+        <v>0.8388316515769387</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.528980491597313</v>
+        <v>8.141299560161073</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1527105153460408</v>
+        <v>0.1525413159944182</v>
       </c>
       <c r="C24">
-        <v>452.9028263259959</v>
+        <v>449.2526274947896</v>
       </c>
       <c r="D24">
-        <v>521.5968263259959</v>
+        <v>522.4236274947897</v>
       </c>
       <c r="E24">
-        <v>-79.30600000000001</v>
+        <v>-74.82900000000001</v>
       </c>
       <c r="F24">
-        <v>98.494</v>
+        <v>102.971</v>
       </c>
       <c r="G24">
         <v>29.8</v>
@@ -3249,28 +3249,28 @@
         <v>42.9</v>
       </c>
       <c r="M24">
-        <v>5.269429</v>
+        <v>5.5089485</v>
       </c>
       <c r="N24">
-        <v>37.630571</v>
+        <v>37.3910515</v>
       </c>
       <c r="O24">
-        <v>5.644585649999999</v>
+        <v>5.608657725</v>
       </c>
       <c r="P24">
-        <v>31.98598535</v>
+        <v>31.782393775</v>
       </c>
       <c r="Q24">
-        <v>49.08598535</v>
+        <v>48.882393775</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1829564299308215</v>
+        <v>0.1845221636291145</v>
       </c>
       <c r="T24">
-        <v>0.8388316515769387</v>
+        <v>0.8484074839657755</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.141299560161073</v>
+        <v>7.787330014067113</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1525413159944182</v>
+        <v>0.1525353166427956</v>
       </c>
       <c r="C25">
-        <v>449.2526274947896</v>
+        <v>444.8049917496201</v>
       </c>
       <c r="D25">
-        <v>522.4236274947897</v>
+        <v>522.4529917496201</v>
       </c>
       <c r="E25">
-        <v>-74.82900000000001</v>
+        <v>-70.352</v>
       </c>
       <c r="F25">
-        <v>102.971</v>
+        <v>107.448</v>
       </c>
       <c r="G25">
         <v>29.8</v>
@@ -3331,45 +3331,45 @@
         <v>42.9</v>
       </c>
       <c r="M25">
-        <v>5.5089485</v>
+        <v>5.834426400000001</v>
       </c>
       <c r="N25">
-        <v>37.3910515</v>
+        <v>37.0655736</v>
       </c>
       <c r="O25">
-        <v>5.608657725</v>
+        <v>5.55983604</v>
       </c>
       <c r="P25">
-        <v>31.782393775</v>
+        <v>31.50573756</v>
       </c>
       <c r="Q25">
-        <v>48.882393775</v>
+        <v>48.60573756</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1845221636291145</v>
+        <v>0.1861291008457837</v>
       </c>
       <c r="T25">
-        <v>0.8484074839657755</v>
+        <v>0.8582353119437922</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.787330014067113</v>
+        <v>7.352907905394092</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1525353166427956</v>
+        <v>0.152372917291173</v>
       </c>
       <c r="C26">
-        <v>444.8049917496201</v>
+        <v>441.1241229738561</v>
       </c>
       <c r="D26">
-        <v>522.4529917496201</v>
+        <v>523.2491229738562</v>
       </c>
       <c r="E26">
-        <v>-70.35200000000002</v>
+        <v>-65.87500000000001</v>
       </c>
       <c r="F26">
-        <v>107.448</v>
+        <v>111.925</v>
       </c>
       <c r="G26">
         <v>29.8</v>
@@ -3413,28 +3413,28 @@
         <v>42.9</v>
       </c>
       <c r="M26">
-        <v>5.8344264</v>
+        <v>6.0775275</v>
       </c>
       <c r="N26">
-        <v>37.0655736</v>
+        <v>36.8224725</v>
       </c>
       <c r="O26">
-        <v>5.55983604</v>
+        <v>5.523370874999999</v>
       </c>
       <c r="P26">
-        <v>31.50573756</v>
+        <v>31.299101625</v>
       </c>
       <c r="Q26">
-        <v>48.60573756</v>
+        <v>48.399101625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1861291008457837</v>
+        <v>0.187778889721564</v>
       </c>
       <c r="T26">
-        <v>0.8582353119437922</v>
+        <v>0.868325215334556</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.352907905394093</v>
+        <v>7.058791589178329</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.152372917291173</v>
+        <v>0.1522105179395503</v>
       </c>
       <c r="C27">
-        <v>441.1241229738561</v>
+        <v>437.4456842434886</v>
       </c>
       <c r="D27">
-        <v>523.2491229738562</v>
+        <v>524.0476842434887</v>
       </c>
       <c r="E27">
-        <v>-65.87500000000001</v>
+        <v>-61.39800000000001</v>
       </c>
       <c r="F27">
-        <v>111.925</v>
+        <v>116.402</v>
       </c>
       <c r="G27">
         <v>29.8</v>
@@ -3495,28 +3495,28 @@
         <v>42.9</v>
       </c>
       <c r="M27">
-        <v>6.0775275</v>
+        <v>6.3206286</v>
       </c>
       <c r="N27">
-        <v>36.8224725</v>
+        <v>36.5793714</v>
       </c>
       <c r="O27">
-        <v>5.523370874999999</v>
+        <v>5.486905709999999</v>
       </c>
       <c r="P27">
-        <v>31.299101625</v>
+        <v>31.09246569</v>
       </c>
       <c r="Q27">
-        <v>48.399101625</v>
+        <v>48.19246569000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.187778889721564</v>
+        <v>0.1894732674858789</v>
       </c>
       <c r="T27">
-        <v>0.868325215334556</v>
+        <v>0.878687818816962</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.058791589178329</v>
+        <v>6.787299604979163</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1522105179395503</v>
+        <v>0.1520481185879277</v>
       </c>
       <c r="C28">
-        <v>437.4456842434886</v>
+        <v>433.7696867014289</v>
       </c>
       <c r="D28">
-        <v>524.0476842434887</v>
+        <v>524.848686701429</v>
       </c>
       <c r="E28">
-        <v>-61.39800000000001</v>
+        <v>-56.92100000000001</v>
       </c>
       <c r="F28">
-        <v>116.402</v>
+        <v>120.879</v>
       </c>
       <c r="G28">
         <v>29.8</v>
@@ -3577,28 +3577,28 @@
         <v>42.9</v>
       </c>
       <c r="M28">
-        <v>6.3206286</v>
+        <v>6.563729700000001</v>
       </c>
       <c r="N28">
-        <v>36.5793714</v>
+        <v>36.3362703</v>
       </c>
       <c r="O28">
-        <v>5.486905709999999</v>
+        <v>5.450440544999999</v>
       </c>
       <c r="P28">
-        <v>31.09246569</v>
+        <v>30.885829755</v>
       </c>
       <c r="Q28">
-        <v>48.19246569000001</v>
+        <v>47.985829755</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1894732674858789</v>
+        <v>0.1912140665588052</v>
       </c>
       <c r="T28">
-        <v>0.878687818816962</v>
+        <v>0.8893343292440917</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.787299604979163</v>
+        <v>6.535918138128082</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1520481185879277</v>
+        <v>0.1518857192363052</v>
       </c>
       <c r="C29">
-        <v>433.7696867014289</v>
+        <v>430.0961415588205</v>
       </c>
       <c r="D29">
-        <v>524.848686701429</v>
+        <v>525.6521415588205</v>
       </c>
       <c r="E29">
-        <v>-56.92100000000001</v>
+        <v>-52.444</v>
       </c>
       <c r="F29">
-        <v>120.879</v>
+        <v>125.356</v>
       </c>
       <c r="G29">
         <v>29.8</v>
@@ -3659,28 +3659,28 @@
         <v>42.9</v>
       </c>
       <c r="M29">
-        <v>6.563729700000001</v>
+        <v>6.8068308</v>
       </c>
       <c r="N29">
-        <v>36.3362703</v>
+        <v>36.0931692</v>
       </c>
       <c r="O29">
-        <v>5.450440544999999</v>
+        <v>5.413975379999999</v>
       </c>
       <c r="P29">
-        <v>30.885829755</v>
+        <v>30.67919382</v>
       </c>
       <c r="Q29">
-        <v>47.985829755</v>
+        <v>47.77919382</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1912140665588052</v>
+        <v>0.193003221161535</v>
       </c>
       <c r="T29">
-        <v>0.8893343292440917</v>
+        <v>0.9002765760719749</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.535918138128082</v>
+        <v>6.302492490337793</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1518857192363052</v>
+        <v>0.1519698198846825</v>
       </c>
       <c r="C30">
-        <v>430.0961415588205</v>
+        <v>425.202755000248</v>
       </c>
       <c r="D30">
-        <v>525.6521415588205</v>
+        <v>525.235755000248</v>
       </c>
       <c r="E30">
-        <v>-52.444</v>
+        <v>-47.96700000000001</v>
       </c>
       <c r="F30">
-        <v>125.356</v>
+        <v>129.833</v>
       </c>
       <c r="G30">
         <v>29.8</v>
@@ -3741,45 +3741,45 @@
         <v>42.9</v>
       </c>
       <c r="M30">
-        <v>6.8068308</v>
+        <v>7.1797649</v>
       </c>
       <c r="N30">
-        <v>36.0931692</v>
+        <v>35.7202351</v>
       </c>
       <c r="O30">
-        <v>5.413975379999999</v>
+        <v>5.358035264999999</v>
       </c>
       <c r="P30">
-        <v>30.67919382</v>
+        <v>30.362199835</v>
       </c>
       <c r="Q30">
-        <v>47.77919382</v>
+        <v>47.462199835</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.193003221161535</v>
+        <v>0.1948427744854684</v>
       </c>
       <c r="T30">
-        <v>0.9002765760719749</v>
+        <v>0.9115270552048688</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.302492490337793</v>
+        <v>5.975126010045258</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1519698198846825</v>
+        <v>0.1518159205330599</v>
       </c>
       <c r="C31">
-        <v>425.202755000248</v>
+        <v>421.4882201256472</v>
       </c>
       <c r="D31">
-        <v>525.235755000248</v>
+        <v>525.9982201256472</v>
       </c>
       <c r="E31">
-        <v>-47.96700000000001</v>
+        <v>-43.49000000000001</v>
       </c>
       <c r="F31">
-        <v>129.833</v>
+        <v>134.31</v>
       </c>
       <c r="G31">
         <v>29.8</v>
@@ -3823,28 +3823,28 @@
         <v>42.9</v>
       </c>
       <c r="M31">
-        <v>7.1797649</v>
+        <v>7.427343</v>
       </c>
       <c r="N31">
-        <v>35.7202351</v>
+        <v>35.472657</v>
       </c>
       <c r="O31">
-        <v>5.358035264999999</v>
+        <v>5.32089855</v>
       </c>
       <c r="P31">
-        <v>30.362199835</v>
+        <v>30.15175845</v>
       </c>
       <c r="Q31">
-        <v>47.462199835</v>
+        <v>47.25175845</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1948427744854684</v>
+        <v>0.1967348864757999</v>
       </c>
       <c r="T31">
-        <v>0.9115270552048688</v>
+        <v>0.9230989765987024</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.975126010045258</v>
+        <v>5.77595514304375</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1518159205330599</v>
+        <v>0.1516620211814373</v>
       </c>
       <c r="C32">
-        <v>421.4882201256472</v>
+        <v>417.7759021535222</v>
       </c>
       <c r="D32">
-        <v>525.9982201256472</v>
+        <v>526.7629021535223</v>
       </c>
       <c r="E32">
-        <v>-43.49000000000001</v>
+        <v>-39.01300000000001</v>
       </c>
       <c r="F32">
-        <v>134.31</v>
+        <v>138.787</v>
       </c>
       <c r="G32">
         <v>29.8</v>
@@ -3905,28 +3905,28 @@
         <v>42.9</v>
       </c>
       <c r="M32">
-        <v>7.427343</v>
+        <v>7.674921100000001</v>
       </c>
       <c r="N32">
-        <v>35.472657</v>
+        <v>35.2250789</v>
       </c>
       <c r="O32">
-        <v>5.32089855</v>
+        <v>5.283761835</v>
       </c>
       <c r="P32">
-        <v>30.15175845</v>
+        <v>29.941317065</v>
       </c>
       <c r="Q32">
-        <v>47.25175845</v>
+        <v>47.041317065</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1967348864757999</v>
+        <v>0.1986818422919382</v>
       </c>
       <c r="T32">
-        <v>0.9230989765987024</v>
+        <v>0.9350063160039517</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.77595514304375</v>
+        <v>5.589634009397177</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1516620211814373</v>
+        <v>0.1515081218298147</v>
       </c>
       <c r="C33">
-        <v>417.7759021535222</v>
+        <v>414.065810766569</v>
       </c>
       <c r="D33">
-        <v>526.7629021535223</v>
+        <v>527.5298107665691</v>
       </c>
       <c r="E33">
-        <v>-39.01300000000001</v>
+        <v>-34.536</v>
       </c>
       <c r="F33">
-        <v>138.787</v>
+        <v>143.264</v>
       </c>
       <c r="G33">
         <v>29.8</v>
@@ -3987,28 +3987,28 @@
         <v>42.9</v>
       </c>
       <c r="M33">
-        <v>7.674921100000001</v>
+        <v>7.922499200000001</v>
       </c>
       <c r="N33">
-        <v>35.2250789</v>
+        <v>34.9775008</v>
       </c>
       <c r="O33">
-        <v>5.283761835</v>
+        <v>5.24662512</v>
       </c>
       <c r="P33">
-        <v>29.941317065</v>
+        <v>29.73087568</v>
       </c>
       <c r="Q33">
-        <v>47.041317065</v>
+        <v>46.83087568000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1986818422919382</v>
+        <v>0.2006860615144334</v>
       </c>
       <c r="T33">
-        <v>0.9350063160039517</v>
+        <v>0.9472638712740611</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.589634009397177</v>
+        <v>5.414957946603516</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1515081218298147</v>
+        <v>0.1513542224781921</v>
       </c>
       <c r="C34">
-        <v>414.065810766569</v>
+        <v>410.3579557039526</v>
       </c>
       <c r="D34">
-        <v>527.5298107665691</v>
+        <v>528.2989557039526</v>
       </c>
       <c r="E34">
-        <v>-34.536</v>
+        <v>-30.059</v>
       </c>
       <c r="F34">
-        <v>143.264</v>
+        <v>147.741</v>
       </c>
       <c r="G34">
         <v>29.8</v>
@@ -4069,28 +4069,28 @@
         <v>42.9</v>
       </c>
       <c r="M34">
-        <v>7.922499200000001</v>
+        <v>8.170077300000001</v>
       </c>
       <c r="N34">
-        <v>34.9775008</v>
+        <v>34.7299227</v>
       </c>
       <c r="O34">
-        <v>5.24662512</v>
+        <v>5.209488404999999</v>
       </c>
       <c r="P34">
-        <v>29.73087568</v>
+        <v>29.520434295</v>
       </c>
       <c r="Q34">
-        <v>46.83087568000001</v>
+        <v>46.620434295</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2006860615144334</v>
+        <v>0.2027501081764062</v>
       </c>
       <c r="T34">
-        <v>0.9472638712740611</v>
+        <v>0.9598873237164127</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.414957946603516</v>
+        <v>5.250868311857954</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1513542224781921</v>
+        <v>0.1512003231265695</v>
       </c>
       <c r="C35">
-        <v>410.3579557039526</v>
+        <v>406.6523467617209</v>
       </c>
       <c r="D35">
-        <v>528.2989557039526</v>
+        <v>529.070346761721</v>
       </c>
       <c r="E35">
-        <v>-30.059</v>
+        <v>-25.58199999999999</v>
       </c>
       <c r="F35">
-        <v>147.741</v>
+        <v>152.218</v>
       </c>
       <c r="G35">
         <v>29.8</v>
@@ -4151,28 +4151,28 @@
         <v>42.9</v>
       </c>
       <c r="M35">
-        <v>8.170077300000001</v>
+        <v>8.417655400000001</v>
       </c>
       <c r="N35">
-        <v>34.7299227</v>
+        <v>34.4823446</v>
       </c>
       <c r="O35">
-        <v>5.209488404999999</v>
+        <v>5.172351689999999</v>
       </c>
       <c r="P35">
-        <v>29.520434295</v>
+        <v>29.30999291</v>
       </c>
       <c r="Q35">
-        <v>46.620434295</v>
+        <v>46.40999291</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2027501081764062</v>
+        <v>0.2048767017069235</v>
       </c>
       <c r="T35">
-        <v>0.9598873237164127</v>
+        <v>0.9728933050206537</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.250868311857954</v>
+        <v>5.096431008568015</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1512003231265695</v>
+        <v>0.1510464237749469</v>
       </c>
       <c r="C36">
-        <v>406.6523467617209</v>
+        <v>402.94899379322</v>
       </c>
       <c r="D36">
-        <v>529.070346761721</v>
+        <v>529.8439937932201</v>
       </c>
       <c r="E36">
-        <v>-25.58199999999999</v>
+        <v>-21.10499999999999</v>
       </c>
       <c r="F36">
-        <v>152.218</v>
+        <v>156.695</v>
       </c>
       <c r="G36">
         <v>29.8</v>
@@ -4233,28 +4233,28 @@
         <v>42.9</v>
       </c>
       <c r="M36">
-        <v>8.417655400000001</v>
+        <v>8.665233500000001</v>
       </c>
       <c r="N36">
-        <v>34.4823446</v>
+        <v>34.2347665</v>
       </c>
       <c r="O36">
-        <v>5.172351689999999</v>
+        <v>5.135214974999999</v>
       </c>
       <c r="P36">
-        <v>29.30999291</v>
+        <v>29.099551525</v>
       </c>
       <c r="Q36">
-        <v>46.40999291</v>
+        <v>46.199551525</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2048767017069235</v>
+        <v>0.2070687288845337</v>
       </c>
       <c r="T36">
-        <v>0.9728933050206537</v>
+        <v>0.9862994703650253</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.096431008568015</v>
+        <v>4.950818694037499</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1510464237749469</v>
+        <v>0.1508925244233243</v>
       </c>
       <c r="C37">
-        <v>402.94899379322</v>
+        <v>399.247906709513</v>
       </c>
       <c r="D37">
-        <v>529.8439937932201</v>
+        <v>530.6199067095131</v>
       </c>
       <c r="E37">
-        <v>-21.10499999999999</v>
+        <v>-16.62799999999999</v>
       </c>
       <c r="F37">
-        <v>156.695</v>
+        <v>161.172</v>
       </c>
       <c r="G37">
         <v>29.8</v>
@@ -4315,28 +4315,28 @@
         <v>42.9</v>
       </c>
       <c r="M37">
-        <v>8.665233500000001</v>
+        <v>8.912811600000001</v>
       </c>
       <c r="N37">
-        <v>34.2347665</v>
+        <v>33.98718839999999</v>
       </c>
       <c r="O37">
-        <v>5.135214974999999</v>
+        <v>5.098078259999999</v>
       </c>
       <c r="P37">
-        <v>29.099551525</v>
+        <v>28.88911014</v>
       </c>
       <c r="Q37">
-        <v>46.199551525</v>
+        <v>45.98911013999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2070687288845337</v>
+        <v>0.2093292569114442</v>
       </c>
       <c r="T37">
-        <v>0.9862994703650253</v>
+        <v>1.000124578376408</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.950818694037499</v>
+        <v>4.813295952536458</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1508925244233243</v>
+        <v>0.1507386250717017</v>
       </c>
       <c r="C38">
-        <v>399.2479067095132</v>
+        <v>395.5490954798049</v>
       </c>
       <c r="D38">
-        <v>530.6199067095133</v>
+        <v>531.398095479805</v>
       </c>
       <c r="E38">
-        <v>-16.62800000000001</v>
+        <v>-12.15100000000001</v>
       </c>
       <c r="F38">
-        <v>161.172</v>
+        <v>165.649</v>
       </c>
       <c r="G38">
         <v>29.8</v>
@@ -4397,28 +4397,28 @@
         <v>42.9</v>
       </c>
       <c r="M38">
-        <v>8.9128116</v>
+        <v>9.1603897</v>
       </c>
       <c r="N38">
-        <v>33.9871884</v>
+        <v>33.7396103</v>
       </c>
       <c r="O38">
-        <v>5.09807826</v>
+        <v>5.060941544999999</v>
       </c>
       <c r="P38">
-        <v>28.88911014</v>
+        <v>28.678668755</v>
       </c>
       <c r="Q38">
-        <v>45.98911014</v>
+        <v>45.778668755</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2093292569114442</v>
+        <v>0.2116615477328598</v>
       </c>
       <c r="T38">
-        <v>1.000124578376408</v>
+        <v>1.014388578705613</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.813295952536459</v>
+        <v>4.683206872738175</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1507386250717017</v>
+        <v>0.1505847257200791</v>
       </c>
       <c r="C39">
-        <v>395.5490954798049</v>
+        <v>391.8525701318671</v>
       </c>
       <c r="D39">
-        <v>531.398095479805</v>
+        <v>532.1785701318671</v>
       </c>
       <c r="E39">
-        <v>-12.15100000000001</v>
+        <v>-7.674000000000007</v>
       </c>
       <c r="F39">
-        <v>165.649</v>
+        <v>170.126</v>
       </c>
       <c r="G39">
         <v>29.8</v>
@@ -4479,28 +4479,28 @@
         <v>42.9</v>
       </c>
       <c r="M39">
-        <v>9.1603897</v>
+        <v>9.4079678</v>
       </c>
       <c r="N39">
-        <v>33.7396103</v>
+        <v>33.4920322</v>
       </c>
       <c r="O39">
-        <v>5.060941544999999</v>
+        <v>5.02380483</v>
       </c>
       <c r="P39">
-        <v>28.678668755</v>
+        <v>28.46822737</v>
       </c>
       <c r="Q39">
-        <v>45.778668755</v>
+        <v>45.56822737</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2116615477328598</v>
+        <v>0.214069073742063</v>
       </c>
       <c r="T39">
-        <v>1.014388578705613</v>
+        <v>1.029112708077695</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.683206872738175</v>
+        <v>4.559964586613487</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1505847257200791</v>
+        <v>0.1512595763684565</v>
       </c>
       <c r="C40">
-        <v>391.8525701318671</v>
+        <v>383.97008467978</v>
       </c>
       <c r="D40">
-        <v>532.1785701318671</v>
+        <v>528.77308467978</v>
       </c>
       <c r="E40">
-        <v>-7.674000000000007</v>
+        <v>-3.197000000000003</v>
       </c>
       <c r="F40">
-        <v>170.126</v>
+        <v>174.603</v>
       </c>
       <c r="G40">
         <v>29.8</v>
@@ -4561,45 +4561,45 @@
         <v>42.9</v>
       </c>
       <c r="M40">
-        <v>9.4079678</v>
+        <v>10.0920534</v>
       </c>
       <c r="N40">
-        <v>33.4920322</v>
+        <v>32.80794659999999</v>
       </c>
       <c r="O40">
-        <v>5.02380483</v>
+        <v>4.921191989999999</v>
       </c>
       <c r="P40">
-        <v>28.46822737</v>
+        <v>27.88675461</v>
       </c>
       <c r="Q40">
-        <v>45.56822737</v>
+        <v>44.98675461</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.214069073742063</v>
+        <v>0.2165555350302565</v>
       </c>
       <c r="T40">
-        <v>1.029112708077695</v>
+        <v>1.044319595789846</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.559964586613487</v>
+        <v>4.250869302772416</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1512595763684565</v>
+        <v>0.1511269270168339</v>
       </c>
       <c r="C41">
-        <v>383.97008467978</v>
+        <v>380.1590246138963</v>
       </c>
       <c r="D41">
-        <v>528.77308467978</v>
+        <v>529.4390246138964</v>
       </c>
       <c r="E41">
-        <v>-3.197000000000003</v>
+        <v>1.280000000000001</v>
       </c>
       <c r="F41">
-        <v>174.603</v>
+        <v>179.08</v>
       </c>
       <c r="G41">
         <v>29.8</v>
@@ -4643,28 +4643,28 @@
         <v>42.9</v>
       </c>
       <c r="M41">
-        <v>10.0920534</v>
+        <v>10.350824</v>
       </c>
       <c r="N41">
-        <v>32.80794659999999</v>
+        <v>32.549176</v>
       </c>
       <c r="O41">
-        <v>4.921191989999999</v>
+        <v>4.882376399999999</v>
       </c>
       <c r="P41">
-        <v>27.88675461</v>
+        <v>27.6667996</v>
       </c>
       <c r="Q41">
-        <v>44.98675461</v>
+        <v>44.7667996</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2165555350302565</v>
+        <v>0.2191248783613898</v>
       </c>
       <c r="T41">
-        <v>1.044319595789846</v>
+        <v>1.060033379759068</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.250869302772416</v>
+        <v>4.144597570203105</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1511269270168339</v>
+        <v>0.1509942776652113</v>
       </c>
       <c r="C42">
-        <v>380.1590246138963</v>
+        <v>376.3496440405181</v>
       </c>
       <c r="D42">
-        <v>529.4390246138964</v>
+        <v>530.1066440405182</v>
       </c>
       <c r="E42">
-        <v>1.280000000000001</v>
+        <v>5.757000000000005</v>
       </c>
       <c r="F42">
-        <v>179.08</v>
+        <v>183.557</v>
       </c>
       <c r="G42">
         <v>29.8</v>
@@ -4725,28 +4725,28 @@
         <v>42.9</v>
       </c>
       <c r="M42">
-        <v>10.350824</v>
+        <v>10.6095946</v>
       </c>
       <c r="N42">
-        <v>32.549176</v>
+        <v>32.2904054</v>
       </c>
       <c r="O42">
-        <v>4.882376399999999</v>
+        <v>4.84356081</v>
       </c>
       <c r="P42">
-        <v>27.6667996</v>
+        <v>27.44684459</v>
       </c>
       <c r="Q42">
-        <v>44.7667996</v>
+        <v>44.54684459</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2191248783613898</v>
+        <v>0.2217813180766292</v>
       </c>
       <c r="T42">
-        <v>1.060033379759068</v>
+        <v>1.076279834371315</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.144597570203105</v>
+        <v>4.043509824588396</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1509942776652113</v>
+        <v>0.1521111283135886</v>
       </c>
       <c r="C43">
-        <v>376.3496440405181</v>
+        <v>366.3036132297508</v>
       </c>
       <c r="D43">
-        <v>530.1066440405182</v>
+        <v>524.5376132297508</v>
       </c>
       <c r="E43">
-        <v>5.757000000000005</v>
+        <v>10.23400000000001</v>
       </c>
       <c r="F43">
-        <v>183.557</v>
+        <v>188.034</v>
       </c>
       <c r="G43">
         <v>29.8</v>
@@ -4807,45 +4807,45 @@
         <v>42.9</v>
       </c>
       <c r="M43">
-        <v>10.6095946</v>
+        <v>11.5264842</v>
       </c>
       <c r="N43">
-        <v>32.2904054</v>
+        <v>31.3735158</v>
       </c>
       <c r="O43">
-        <v>4.84356081</v>
+        <v>4.70602737</v>
       </c>
       <c r="P43">
-        <v>27.44684459</v>
+        <v>26.66748843</v>
       </c>
       <c r="Q43">
-        <v>44.54684459</v>
+        <v>43.76748843</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2217813180766292</v>
+        <v>0.2245293591613597</v>
       </c>
       <c r="T43">
-        <v>1.076279834371315</v>
+        <v>1.093086511556398</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.043509824588396</v>
+        <v>3.721863428225582</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1521111283135886</v>
+        <v>0.152008228961966</v>
       </c>
       <c r="C44">
-        <v>366.3036132297508</v>
+        <v>362.3348090713587</v>
       </c>
       <c r="D44">
-        <v>524.5376132297508</v>
+        <v>525.0458090713587</v>
       </c>
       <c r="E44">
-        <v>10.23399999999998</v>
+        <v>14.71099999999998</v>
       </c>
       <c r="F44">
-        <v>188.034</v>
+        <v>192.511</v>
       </c>
       <c r="G44">
         <v>29.8</v>
@@ -4889,28 +4889,28 @@
         <v>42.9</v>
       </c>
       <c r="M44">
-        <v>11.5264842</v>
+        <v>11.8009243</v>
       </c>
       <c r="N44">
-        <v>31.3735158</v>
+        <v>31.0990757</v>
       </c>
       <c r="O44">
-        <v>4.70602737</v>
+        <v>4.664861355</v>
       </c>
       <c r="P44">
-        <v>26.66748843</v>
+        <v>26.434214345</v>
       </c>
       <c r="Q44">
-        <v>43.76748843</v>
+        <v>43.534214345</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2245293591613597</v>
+        <v>0.2273738227402913</v>
       </c>
       <c r="T44">
-        <v>1.093086511556398</v>
+        <v>1.110482896712887</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.721863428225582</v>
+        <v>3.635308464778475</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.152008228961966</v>
+        <v>0.1519053296103434</v>
       </c>
       <c r="C45">
-        <v>362.3348090713587</v>
+        <v>358.3669905943228</v>
       </c>
       <c r="D45">
-        <v>525.0458090713587</v>
+        <v>525.5549905943228</v>
       </c>
       <c r="E45">
-        <v>14.71099999999998</v>
+        <v>19.18799999999999</v>
       </c>
       <c r="F45">
-        <v>192.511</v>
+        <v>196.988</v>
       </c>
       <c r="G45">
         <v>29.8</v>
@@ -4971,28 +4971,28 @@
         <v>42.9</v>
       </c>
       <c r="M45">
-        <v>11.8009243</v>
+        <v>12.0753644</v>
       </c>
       <c r="N45">
-        <v>31.0990757</v>
+        <v>30.8246356</v>
       </c>
       <c r="O45">
-        <v>4.664861355</v>
+        <v>4.62369534</v>
       </c>
       <c r="P45">
-        <v>26.434214345</v>
+        <v>26.20094026</v>
       </c>
       <c r="Q45">
-        <v>43.534214345</v>
+        <v>43.30094026</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2273738227402913</v>
+        <v>0.2303198743041847</v>
       </c>
       <c r="T45">
-        <v>1.110482896712887</v>
+        <v>1.128500581339251</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.635308464778475</v>
+        <v>3.552687817851691</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1519053296103434</v>
+        <v>0.1528734302587208</v>
       </c>
       <c r="C46">
-        <v>358.3669905943228</v>
+        <v>349.1382036577975</v>
       </c>
       <c r="D46">
-        <v>525.5549905943228</v>
+        <v>520.8032036577976</v>
       </c>
       <c r="E46">
-        <v>19.18799999999999</v>
+        <v>23.66499999999999</v>
       </c>
       <c r="F46">
-        <v>196.988</v>
+        <v>201.465</v>
       </c>
       <c r="G46">
         <v>29.8</v>
@@ -5053,45 +5053,45 @@
         <v>42.9</v>
       </c>
       <c r="M46">
-        <v>12.0753644</v>
+        <v>12.9139065</v>
       </c>
       <c r="N46">
-        <v>30.8246356</v>
+        <v>29.9860935</v>
       </c>
       <c r="O46">
-        <v>4.62369534</v>
+        <v>4.497914024999999</v>
       </c>
       <c r="P46">
-        <v>26.20094026</v>
+        <v>25.488179475</v>
       </c>
       <c r="Q46">
-        <v>43.30094026</v>
+        <v>42.588179475</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2303198743041847</v>
+        <v>0.233373055015856</v>
       </c>
       <c r="T46">
-        <v>1.128500581339251</v>
+        <v>1.147173454497483</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.552687817851691</v>
+        <v>3.322000201875396</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1528734302587208</v>
+        <v>0.1527943309070982</v>
       </c>
       <c r="C47">
-        <v>349.1382036577975</v>
+        <v>345.0462258863871</v>
       </c>
       <c r="D47">
-        <v>520.8032036577976</v>
+        <v>521.1882258863872</v>
       </c>
       <c r="E47">
-        <v>23.66499999999999</v>
+        <v>28.142</v>
       </c>
       <c r="F47">
-        <v>201.465</v>
+        <v>205.942</v>
       </c>
       <c r="G47">
         <v>29.8</v>
@@ -5135,28 +5135,28 @@
         <v>42.9</v>
       </c>
       <c r="M47">
-        <v>12.9139065</v>
+        <v>13.2008822</v>
       </c>
       <c r="N47">
-        <v>29.9860935</v>
+        <v>29.6991178</v>
       </c>
       <c r="O47">
-        <v>4.497914024999999</v>
+        <v>4.45486767</v>
       </c>
       <c r="P47">
-        <v>25.488179475</v>
+        <v>25.24425013</v>
       </c>
       <c r="Q47">
-        <v>42.588179475</v>
+        <v>42.34425013</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.233373055015856</v>
+        <v>0.2365393164946263</v>
       </c>
       <c r="T47">
-        <v>1.147173454497483</v>
+        <v>1.166537915550464</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.322000201875396</v>
+        <v>3.249782806182453</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1527943309070982</v>
+        <v>0.1527152315554756</v>
       </c>
       <c r="C48">
-        <v>345.0462258863871</v>
+        <v>340.9548178188104</v>
       </c>
       <c r="D48">
-        <v>521.1882258863872</v>
+        <v>521.5738178188104</v>
       </c>
       <c r="E48">
-        <v>28.142</v>
+        <v>32.619</v>
       </c>
       <c r="F48">
-        <v>205.942</v>
+        <v>210.419</v>
       </c>
       <c r="G48">
         <v>29.8</v>
@@ -5217,28 +5217,28 @@
         <v>42.9</v>
       </c>
       <c r="M48">
-        <v>13.2008822</v>
+        <v>13.4878579</v>
       </c>
       <c r="N48">
-        <v>29.6991178</v>
+        <v>29.4121421</v>
       </c>
       <c r="O48">
-        <v>4.45486767</v>
+        <v>4.411821314999999</v>
       </c>
       <c r="P48">
-        <v>25.24425013</v>
+        <v>25.000320785</v>
       </c>
       <c r="Q48">
-        <v>42.34425013</v>
+        <v>42.100320785</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2365393164946263</v>
+        <v>0.2398250595386332</v>
       </c>
       <c r="T48">
-        <v>1.166537915550464</v>
+        <v>1.186633110982803</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.249782806182453</v>
+        <v>3.180638491157294</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1527152315554756</v>
+        <v>0.152636132203853</v>
       </c>
       <c r="C49">
-        <v>340.9548178188104</v>
+        <v>336.8639807204594</v>
       </c>
       <c r="D49">
-        <v>521.5738178188104</v>
+        <v>521.9599807204595</v>
       </c>
       <c r="E49">
-        <v>32.619</v>
+        <v>37.096</v>
       </c>
       <c r="F49">
-        <v>210.419</v>
+        <v>214.896</v>
       </c>
       <c r="G49">
         <v>29.8</v>
@@ -5299,28 +5299,28 @@
         <v>42.9</v>
       </c>
       <c r="M49">
-        <v>13.4878579</v>
+        <v>13.7748336</v>
       </c>
       <c r="N49">
-        <v>29.4121421</v>
+        <v>29.1251664</v>
       </c>
       <c r="O49">
-        <v>4.411821314999999</v>
+        <v>4.36877496</v>
       </c>
       <c r="P49">
-        <v>25.000320785</v>
+        <v>24.75639144</v>
       </c>
       <c r="Q49">
-        <v>42.100320785</v>
+        <v>41.85639144</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2398250595386332</v>
+        <v>0.2432371773151019</v>
       </c>
       <c r="T49">
-        <v>1.186633110982803</v>
+        <v>1.207501198547155</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.180638491157294</v>
+        <v>3.114375189258184</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.152636132203853</v>
+        <v>0.1525570328522304</v>
       </c>
       <c r="C50">
-        <v>336.8639807204595</v>
+        <v>332.7737158604768</v>
       </c>
       <c r="D50">
-        <v>521.9599807204595</v>
+        <v>522.3467158604768</v>
       </c>
       <c r="E50">
-        <v>37.09599999999998</v>
+        <v>41.57299999999998</v>
       </c>
       <c r="F50">
-        <v>214.896</v>
+        <v>219.373</v>
       </c>
       <c r="G50">
         <v>29.8</v>
@@ -5381,28 +5381,28 @@
         <v>42.9</v>
       </c>
       <c r="M50">
-        <v>13.7748336</v>
+        <v>14.0618093</v>
       </c>
       <c r="N50">
-        <v>29.1251664</v>
+        <v>28.8381907</v>
       </c>
       <c r="O50">
-        <v>4.36877496</v>
+        <v>4.325728604999999</v>
       </c>
       <c r="P50">
-        <v>24.75639144</v>
+        <v>24.512462095</v>
       </c>
       <c r="Q50">
-        <v>41.85639144</v>
+        <v>41.612462095</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2432371773151019</v>
+        <v>0.2467831036318243</v>
       </c>
       <c r="T50">
-        <v>1.207501198547155</v>
+        <v>1.229187642486579</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.114375189258184</v>
+        <v>3.050816511926385</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1525570328522304</v>
+        <v>0.1557929335006078</v>
       </c>
       <c r="C51">
-        <v>332.7737158604768</v>
+        <v>312.9297097925697</v>
       </c>
       <c r="D51">
-        <v>522.3467158604768</v>
+        <v>506.9797097925697</v>
       </c>
       <c r="E51">
-        <v>41.57299999999998</v>
+        <v>46.04999999999998</v>
       </c>
       <c r="F51">
-        <v>219.373</v>
+        <v>223.85</v>
       </c>
       <c r="G51">
         <v>29.8</v>
@@ -5463,45 +5463,45 @@
         <v>42.9</v>
       </c>
       <c r="M51">
-        <v>14.0618093</v>
+        <v>16.094815</v>
       </c>
       <c r="N51">
-        <v>28.8381907</v>
+        <v>26.805185</v>
       </c>
       <c r="O51">
-        <v>4.325728604999999</v>
+        <v>4.02077775</v>
       </c>
       <c r="P51">
-        <v>24.512462095</v>
+        <v>22.78440725</v>
       </c>
       <c r="Q51">
-        <v>41.612462095</v>
+        <v>39.88440725</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2467831036318243</v>
+        <v>0.2504708670012156</v>
       </c>
       <c r="T51">
-        <v>1.229187642486579</v>
+        <v>1.251741544183581</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.15</v>
       </c>
       <c r="W51">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.050816511926385</v>
+        <v>2.665454682144529</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1557929335006078</v>
+        <v>0.1557801341489852</v>
       </c>
       <c r="C52">
-        <v>312.9297097925697</v>
+        <v>308.5117114624746</v>
       </c>
       <c r="D52">
-        <v>506.9797097925697</v>
+        <v>507.0387114624747</v>
       </c>
       <c r="E52">
-        <v>46.04999999999998</v>
+        <v>50.52699999999999</v>
       </c>
       <c r="F52">
-        <v>223.85</v>
+        <v>228.327</v>
       </c>
       <c r="G52">
         <v>29.8</v>
@@ -5545,28 +5545,28 @@
         <v>42.9</v>
       </c>
       <c r="M52">
-        <v>16.094815</v>
+        <v>16.4167113</v>
       </c>
       <c r="N52">
-        <v>26.805185</v>
+        <v>26.4832887</v>
       </c>
       <c r="O52">
-        <v>4.02077775</v>
+        <v>3.972493304999999</v>
       </c>
       <c r="P52">
-        <v>22.78440725</v>
+        <v>22.510795395</v>
       </c>
       <c r="Q52">
-        <v>39.88440725</v>
+        <v>39.610795395</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2504708670012156</v>
+        <v>0.2543091513244596</v>
       </c>
       <c r="T52">
-        <v>1.251741544183581</v>
+        <v>1.275216013296786</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.665454682144529</v>
+        <v>2.613190864847577</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1557801341489852</v>
+        <v>0.1557673347973626</v>
       </c>
       <c r="C53">
-        <v>308.5117114624746</v>
+        <v>304.0937268670604</v>
       </c>
       <c r="D53">
-        <v>507.0387114624747</v>
+        <v>507.0977268670604</v>
       </c>
       <c r="E53">
-        <v>50.52699999999999</v>
+        <v>55.00399999999999</v>
       </c>
       <c r="F53">
-        <v>228.327</v>
+        <v>232.804</v>
       </c>
       <c r="G53">
         <v>29.8</v>
@@ -5627,28 +5627,28 @@
         <v>42.9</v>
       </c>
       <c r="M53">
-        <v>16.4167113</v>
+        <v>16.7386076</v>
       </c>
       <c r="N53">
-        <v>26.4832887</v>
+        <v>26.1613924</v>
       </c>
       <c r="O53">
-        <v>3.972493304999999</v>
+        <v>3.924208859999999</v>
       </c>
       <c r="P53">
-        <v>22.510795395</v>
+        <v>22.23718354</v>
       </c>
       <c r="Q53">
-        <v>39.610795395</v>
+        <v>39.33718354</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2543091513244596</v>
+        <v>0.2583073641611721</v>
       </c>
       <c r="T53">
-        <v>1.275216013296786</v>
+        <v>1.299668585289709</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.613190864847577</v>
+        <v>2.562937194369739</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1557673347973626</v>
+        <v>0.15575453544574</v>
       </c>
       <c r="C54">
-        <v>304.0937268670604</v>
+        <v>299.6757560111234</v>
       </c>
       <c r="D54">
-        <v>507.0977268670604</v>
+        <v>507.1567560111234</v>
       </c>
       <c r="E54">
-        <v>55.00399999999999</v>
+        <v>59.48099999999999</v>
       </c>
       <c r="F54">
-        <v>232.804</v>
+        <v>237.281</v>
       </c>
       <c r="G54">
         <v>29.8</v>
@@ -5709,28 +5709,28 @@
         <v>42.9</v>
       </c>
       <c r="M54">
-        <v>16.7386076</v>
+        <v>17.0605039</v>
       </c>
       <c r="N54">
-        <v>26.1613924</v>
+        <v>25.8394961</v>
       </c>
       <c r="O54">
-        <v>3.924208859999999</v>
+        <v>3.875924415</v>
       </c>
       <c r="P54">
-        <v>22.23718354</v>
+        <v>21.963571685</v>
       </c>
       <c r="Q54">
-        <v>39.33718354</v>
+        <v>39.063571685</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2583073641611721</v>
+        <v>0.2624757137143404</v>
       </c>
       <c r="T54">
-        <v>1.299668585289709</v>
+        <v>1.325161692261054</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.562937194369739</v>
+        <v>2.514579888815593</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.15575453544574</v>
+        <v>0.1575318360941174</v>
       </c>
       <c r="C55">
-        <v>299.6757560111234</v>
+        <v>287.1314936909349</v>
       </c>
       <c r="D55">
-        <v>507.1567560111234</v>
+        <v>499.0894936909349</v>
       </c>
       <c r="E55">
-        <v>59.48099999999999</v>
+        <v>63.958</v>
       </c>
       <c r="F55">
-        <v>237.281</v>
+        <v>241.758</v>
       </c>
       <c r="G55">
         <v>29.8</v>
@@ -5791,45 +5791,45 @@
         <v>42.9</v>
       </c>
       <c r="M55">
-        <v>17.0605039</v>
+        <v>18.3252564</v>
       </c>
       <c r="N55">
-        <v>25.8394961</v>
+        <v>24.5747436</v>
       </c>
       <c r="O55">
-        <v>3.875924415</v>
+        <v>3.68621154</v>
       </c>
       <c r="P55">
-        <v>21.963571685</v>
+        <v>20.88853206</v>
       </c>
       <c r="Q55">
-        <v>39.063571685</v>
+        <v>37.98853206</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2624757137143404</v>
+        <v>0.2668252958567769</v>
       </c>
       <c r="T55">
-        <v>1.325161692261054</v>
+        <v>1.351763195187674</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.15</v>
       </c>
       <c r="W55">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.514579888815593</v>
+        <v>2.341031364778067</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1575318360941174</v>
+        <v>0.1575521867424947</v>
       </c>
       <c r="C56">
-        <v>287.1314936909349</v>
+        <v>282.5636069253959</v>
       </c>
       <c r="D56">
-        <v>499.0894936909349</v>
+        <v>498.9986069253959</v>
       </c>
       <c r="E56">
-        <v>63.958</v>
+        <v>68.435</v>
       </c>
       <c r="F56">
-        <v>241.758</v>
+        <v>246.235</v>
       </c>
       <c r="G56">
         <v>29.8</v>
@@ -5873,28 +5873,28 @@
         <v>42.9</v>
       </c>
       <c r="M56">
-        <v>18.3252564</v>
+        <v>18.664613</v>
       </c>
       <c r="N56">
-        <v>24.5747436</v>
+        <v>24.235387</v>
       </c>
       <c r="O56">
-        <v>3.68621154</v>
+        <v>3.635308049999999</v>
       </c>
       <c r="P56">
-        <v>20.88853206</v>
+        <v>20.60007895</v>
       </c>
       <c r="Q56">
-        <v>37.98853206</v>
+        <v>37.70007895</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2668252958567769</v>
+        <v>0.2713681927610995</v>
       </c>
       <c r="T56">
-        <v>1.351763195187674</v>
+        <v>1.379546987133256</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.341031364778067</v>
+        <v>2.298467158145738</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1575521867424947</v>
+        <v>0.1575725373908721</v>
       </c>
       <c r="C57">
-        <v>282.5636069253959</v>
+        <v>277.9957532557254</v>
       </c>
       <c r="D57">
-        <v>498.9986069253959</v>
+        <v>498.9077532557254</v>
       </c>
       <c r="E57">
-        <v>68.435</v>
+        <v>72.91200000000001</v>
       </c>
       <c r="F57">
-        <v>246.235</v>
+        <v>250.712</v>
       </c>
       <c r="G57">
         <v>29.8</v>
@@ -5955,28 +5955,28 @@
         <v>42.9</v>
       </c>
       <c r="M57">
-        <v>18.664613</v>
+        <v>19.0039696</v>
       </c>
       <c r="N57">
-        <v>24.235387</v>
+        <v>23.8960304</v>
       </c>
       <c r="O57">
-        <v>3.635308049999999</v>
+        <v>3.584404559999999</v>
       </c>
       <c r="P57">
-        <v>20.60007895</v>
+        <v>20.31162584</v>
       </c>
       <c r="Q57">
-        <v>37.70007895</v>
+        <v>37.41162584</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2713681927610995</v>
+        <v>0.2761175849792549</v>
       </c>
       <c r="T57">
-        <v>1.379546987133256</v>
+        <v>1.408593678712727</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.298467158145738</v>
+        <v>2.257423101750279</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1575725373908721</v>
+        <v>0.1575928880392495</v>
       </c>
       <c r="C58">
-        <v>277.9957532557254</v>
+        <v>273.4279326638492</v>
       </c>
       <c r="D58">
-        <v>498.9077532557254</v>
+        <v>498.8169326638492</v>
       </c>
       <c r="E58">
-        <v>72.91200000000001</v>
+        <v>77.38900000000001</v>
       </c>
       <c r="F58">
-        <v>250.712</v>
+        <v>255.189</v>
       </c>
       <c r="G58">
         <v>29.8</v>
@@ -6037,28 +6037,28 @@
         <v>42.9</v>
       </c>
       <c r="M58">
-        <v>19.0039696</v>
+        <v>19.3433262</v>
       </c>
       <c r="N58">
-        <v>23.8960304</v>
+        <v>23.5566738</v>
       </c>
       <c r="O58">
-        <v>3.584404559999999</v>
+        <v>3.533501069999999</v>
       </c>
       <c r="P58">
-        <v>20.31162584</v>
+        <v>20.02317273</v>
       </c>
       <c r="Q58">
-        <v>37.41162584</v>
+        <v>37.12317272999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2761175849792549</v>
+        <v>0.2810878791610454</v>
       </c>
       <c r="T58">
-        <v>1.408593678712727</v>
+        <v>1.438991379202872</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.257423101750279</v>
+        <v>2.217819187684483</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1575928880392495</v>
+        <v>0.1576132386876269</v>
       </c>
       <c r="C59">
-        <v>273.4279326638492</v>
+        <v>268.8601451317065</v>
       </c>
       <c r="D59">
-        <v>498.8169326638492</v>
+        <v>498.7261451317065</v>
       </c>
       <c r="E59">
-        <v>77.38900000000001</v>
+        <v>81.86599999999999</v>
       </c>
       <c r="F59">
-        <v>255.189</v>
+        <v>259.666</v>
       </c>
       <c r="G59">
         <v>29.8</v>
@@ -6119,28 +6119,28 @@
         <v>42.9</v>
       </c>
       <c r="M59">
-        <v>19.3433262</v>
+        <v>19.6826828</v>
       </c>
       <c r="N59">
-        <v>23.5566738</v>
+        <v>23.2173172</v>
       </c>
       <c r="O59">
-        <v>3.533501069999999</v>
+        <v>3.482597579999999</v>
       </c>
       <c r="P59">
-        <v>20.02317273</v>
+        <v>19.73471962</v>
       </c>
       <c r="Q59">
-        <v>37.12317272999999</v>
+        <v>36.83471962</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2810878791610454</v>
+        <v>0.2862948540181594</v>
       </c>
       <c r="T59">
-        <v>1.438991379202872</v>
+        <v>1.470836589240166</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.217819187684483</v>
+        <v>2.179580925827855</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1576132386876269</v>
+        <v>0.1576335893360043</v>
       </c>
       <c r="C60">
-        <v>268.8601451317064</v>
+        <v>264.2923906412494</v>
       </c>
       <c r="D60">
-        <v>498.7261451317064</v>
+        <v>498.6353906412494</v>
       </c>
       <c r="E60">
-        <v>81.86599999999999</v>
+        <v>86.34299999999996</v>
       </c>
       <c r="F60">
-        <v>259.666</v>
+        <v>264.143</v>
       </c>
       <c r="G60">
         <v>29.8</v>
@@ -6201,28 +6201,28 @@
         <v>42.9</v>
       </c>
       <c r="M60">
-        <v>19.6826828</v>
+        <v>20.0220394</v>
       </c>
       <c r="N60">
-        <v>23.2173172</v>
+        <v>22.8779606</v>
       </c>
       <c r="O60">
-        <v>3.482597579999999</v>
+        <v>3.43169409</v>
       </c>
       <c r="P60">
-        <v>19.73471962</v>
+        <v>19.44626651</v>
       </c>
       <c r="Q60">
-        <v>36.83471962</v>
+        <v>36.54626651</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2862948540181594</v>
+        <v>0.291755827648791</v>
       </c>
       <c r="T60">
-        <v>1.470836589240166</v>
+        <v>1.504235224157328</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.179580925827855</v>
+        <v>2.142638876237553</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1576335893360043</v>
+        <v>0.1576539399843817</v>
       </c>
       <c r="C61">
-        <v>264.2923906412494</v>
+        <v>259.7246691744429</v>
       </c>
       <c r="D61">
-        <v>498.6353906412494</v>
+        <v>498.5446691744429</v>
       </c>
       <c r="E61">
-        <v>86.34299999999996</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="F61">
-        <v>264.143</v>
+        <v>268.62</v>
       </c>
       <c r="G61">
         <v>29.8</v>
@@ -6283,28 +6283,28 @@
         <v>42.9</v>
       </c>
       <c r="M61">
-        <v>20.0220394</v>
+        <v>20.361396</v>
       </c>
       <c r="N61">
-        <v>22.8779606</v>
+        <v>22.538604</v>
       </c>
       <c r="O61">
-        <v>3.43169409</v>
+        <v>3.380790599999999</v>
       </c>
       <c r="P61">
-        <v>19.44626651</v>
+        <v>19.15781339999999</v>
       </c>
       <c r="Q61">
-        <v>36.54626651</v>
+        <v>36.2578134</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.291755827648791</v>
+        <v>0.2974898499609542</v>
       </c>
       <c r="T61">
-        <v>1.504235224157328</v>
+        <v>1.539303790820349</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.142638876237553</v>
+        <v>2.106928228300259</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1576539399843817</v>
+        <v>0.1576742906327591</v>
       </c>
       <c r="C62">
-        <v>259.7246691744429</v>
+        <v>255.1569807132654</v>
       </c>
       <c r="D62">
-        <v>498.5446691744429</v>
+        <v>498.4539807132654</v>
       </c>
       <c r="E62">
-        <v>90.81999999999999</v>
+        <v>95.29699999999997</v>
       </c>
       <c r="F62">
-        <v>268.62</v>
+        <v>273.097</v>
       </c>
       <c r="G62">
         <v>29.8</v>
@@ -6365,28 +6365,28 @@
         <v>42.9</v>
       </c>
       <c r="M62">
-        <v>20.361396</v>
+        <v>20.7007526</v>
       </c>
       <c r="N62">
-        <v>22.538604</v>
+        <v>22.1992474</v>
       </c>
       <c r="O62">
-        <v>3.380790599999999</v>
+        <v>3.32988711</v>
       </c>
       <c r="P62">
-        <v>19.15781339999999</v>
+        <v>18.86936029</v>
       </c>
       <c r="Q62">
-        <v>36.2578134</v>
+        <v>35.96936029</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2974898499609542</v>
+        <v>0.3035179246993823</v>
       </c>
       <c r="T62">
-        <v>1.539303790820349</v>
+        <v>1.576170745517371</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.106928228300259</v>
+        <v>2.072388421278944</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1576742906327591</v>
+        <v>0.1576946412811365</v>
       </c>
       <c r="C63">
-        <v>255.1569807132654</v>
+        <v>250.5893252397087</v>
       </c>
       <c r="D63">
-        <v>498.4539807132654</v>
+        <v>498.3633252397087</v>
       </c>
       <c r="E63">
-        <v>95.29699999999997</v>
+        <v>99.774</v>
       </c>
       <c r="F63">
-        <v>273.097</v>
+        <v>277.574</v>
       </c>
       <c r="G63">
         <v>29.8</v>
@@ -6447,28 +6447,28 @@
         <v>42.9</v>
       </c>
       <c r="M63">
-        <v>20.7007526</v>
+        <v>21.0401092</v>
       </c>
       <c r="N63">
-        <v>22.1992474</v>
+        <v>21.8598908</v>
       </c>
       <c r="O63">
-        <v>3.32988711</v>
+        <v>3.278983619999999</v>
       </c>
       <c r="P63">
-        <v>18.86936029</v>
+        <v>18.58090718</v>
       </c>
       <c r="Q63">
-        <v>35.96936029</v>
+        <v>35.68090718</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3035179246993823</v>
+        <v>0.3098632665293066</v>
       </c>
       <c r="T63">
-        <v>1.576170745517371</v>
+        <v>1.614978066251078</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.072388421278944</v>
+        <v>2.038962801580896</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1576946412811365</v>
+        <v>0.1577149919295139</v>
       </c>
       <c r="C64">
-        <v>250.5893252397087</v>
+        <v>246.0217027357772</v>
       </c>
       <c r="D64">
-        <v>498.3633252397087</v>
+        <v>498.2727027357772</v>
       </c>
       <c r="E64">
-        <v>99.774</v>
+        <v>104.251</v>
       </c>
       <c r="F64">
-        <v>277.574</v>
+        <v>282.051</v>
       </c>
       <c r="G64">
         <v>29.8</v>
@@ -6529,28 +6529,28 @@
         <v>42.9</v>
       </c>
       <c r="M64">
-        <v>21.0401092</v>
+        <v>21.3794658</v>
       </c>
       <c r="N64">
-        <v>21.8598908</v>
+        <v>21.5205342</v>
       </c>
       <c r="O64">
-        <v>3.278983619999999</v>
+        <v>3.228080129999999</v>
       </c>
       <c r="P64">
-        <v>18.58090718</v>
+        <v>18.29245407</v>
       </c>
       <c r="Q64">
-        <v>35.68090718</v>
+        <v>35.39245407</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3098632665293066</v>
+        <v>0.316551599809497</v>
       </c>
       <c r="T64">
-        <v>1.614978066251078</v>
+        <v>1.655883079997418</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.038962801580896</v>
+        <v>2.006598312666914</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1577149919295139</v>
+        <v>0.1654601425778913</v>
       </c>
       <c r="C65">
-        <v>246.0217027357772</v>
+        <v>209.2933861024992</v>
       </c>
       <c r="D65">
-        <v>498.2727027357772</v>
+        <v>466.0213861024992</v>
       </c>
       <c r="E65">
-        <v>104.251</v>
+        <v>108.728</v>
       </c>
       <c r="F65">
-        <v>282.051</v>
+        <v>286.528</v>
       </c>
       <c r="G65">
         <v>29.8</v>
@@ -6611,45 +6611,45 @@
         <v>42.9</v>
       </c>
       <c r="M65">
-        <v>21.3794658</v>
+        <v>25.78752</v>
       </c>
       <c r="N65">
-        <v>21.5205342</v>
+        <v>17.11248</v>
       </c>
       <c r="O65">
-        <v>3.228080129999999</v>
+        <v>2.566872</v>
       </c>
       <c r="P65">
-        <v>18.29245407</v>
+        <v>14.545608</v>
       </c>
       <c r="Q65">
-        <v>35.39245407</v>
+        <v>31.645608</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.316551599809497</v>
+        <v>0.3236115071608091</v>
       </c>
       <c r="T65">
-        <v>1.655883079997418</v>
+        <v>1.699060594507443</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.15</v>
       </c>
       <c r="W65">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.006598312666914</v>
+        <v>1.663595413595413</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1654601425778913</v>
+        <v>0.1656011932262687</v>
       </c>
       <c r="C66">
-        <v>209.2933861024992</v>
+        <v>204.2677052680492</v>
       </c>
       <c r="D66">
-        <v>466.0213861024992</v>
+        <v>465.4727052680492</v>
       </c>
       <c r="E66">
-        <v>108.728</v>
+        <v>113.205</v>
       </c>
       <c r="F66">
-        <v>286.528</v>
+        <v>291.005</v>
       </c>
       <c r="G66">
         <v>29.8</v>
@@ -6693,28 +6693,28 @@
         <v>42.9</v>
       </c>
       <c r="M66">
-        <v>25.78752</v>
+        <v>26.19045</v>
       </c>
       <c r="N66">
-        <v>17.11248</v>
+        <v>16.70955</v>
       </c>
       <c r="O66">
-        <v>2.566872</v>
+        <v>2.5064325</v>
       </c>
       <c r="P66">
-        <v>14.545608</v>
+        <v>14.2031175</v>
       </c>
       <c r="Q66">
-        <v>31.645608</v>
+        <v>31.3031175</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3236115071608091</v>
+        <v>0.3310748377893391</v>
       </c>
       <c r="T66">
-        <v>1.699060594507443</v>
+        <v>1.744705395560898</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.663595413595413</v>
+        <v>1.638001638001638</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1656011932262687</v>
+        <v>0.1657422438746461</v>
       </c>
       <c r="C67">
-        <v>204.2677052680492</v>
+        <v>199.2433149178348</v>
       </c>
       <c r="D67">
-        <v>465.4727052680492</v>
+        <v>464.9253149178348</v>
       </c>
       <c r="E67">
-        <v>113.205</v>
+        <v>117.682</v>
       </c>
       <c r="F67">
-        <v>291.005</v>
+        <v>295.482</v>
       </c>
       <c r="G67">
         <v>29.8</v>
@@ -6775,28 +6775,28 @@
         <v>42.9</v>
       </c>
       <c r="M67">
-        <v>26.19045</v>
+        <v>26.59338</v>
       </c>
       <c r="N67">
-        <v>16.70955</v>
+        <v>16.30662</v>
       </c>
       <c r="O67">
-        <v>2.5064325</v>
+        <v>2.445993</v>
       </c>
       <c r="P67">
-        <v>14.2031175</v>
+        <v>13.860627</v>
       </c>
       <c r="Q67">
-        <v>31.3031175</v>
+        <v>30.960627</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3310748377893391</v>
+        <v>0.3389771878666061</v>
       </c>
       <c r="T67">
-        <v>1.744705395560898</v>
+        <v>1.793035184911616</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.638001638001638</v>
+        <v>1.61318343136525</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1657422438746461</v>
+        <v>0.1658832945230235</v>
       </c>
       <c r="C68">
-        <v>199.2433149178348</v>
+        <v>194.2202105044216</v>
       </c>
       <c r="D68">
-        <v>464.9253149178348</v>
+        <v>464.3792105044216</v>
       </c>
       <c r="E68">
-        <v>117.682</v>
+        <v>122.159</v>
       </c>
       <c r="F68">
-        <v>295.482</v>
+        <v>299.959</v>
       </c>
       <c r="G68">
         <v>29.8</v>
@@ -6857,28 +6857,28 @@
         <v>42.9</v>
       </c>
       <c r="M68">
-        <v>26.59338</v>
+        <v>26.99631</v>
       </c>
       <c r="N68">
-        <v>16.30662</v>
+        <v>15.90369</v>
       </c>
       <c r="O68">
-        <v>2.445993</v>
+        <v>2.3855535</v>
       </c>
       <c r="P68">
-        <v>13.860627</v>
+        <v>13.5181365</v>
       </c>
       <c r="Q68">
-        <v>30.960627</v>
+        <v>30.6181365</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3389771878666061</v>
+        <v>0.3473584682515863</v>
       </c>
       <c r="T68">
-        <v>1.793035184911616</v>
+        <v>1.844294052404801</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.61318343136525</v>
+        <v>1.589106066718007</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1658832945230235</v>
+        <v>0.1660243451714009</v>
       </c>
       <c r="C69">
-        <v>194.2202105044216</v>
+        <v>189.1983875017157</v>
       </c>
       <c r="D69">
-        <v>464.3792105044216</v>
+        <v>463.8343875017158</v>
       </c>
       <c r="E69">
-        <v>122.159</v>
+        <v>126.636</v>
       </c>
       <c r="F69">
-        <v>299.959</v>
+        <v>304.436</v>
       </c>
       <c r="G69">
         <v>29.8</v>
@@ -6939,28 +6939,28 @@
         <v>42.9</v>
       </c>
       <c r="M69">
-        <v>26.99631</v>
+        <v>27.39924</v>
       </c>
       <c r="N69">
-        <v>15.90369</v>
+        <v>15.50076</v>
       </c>
       <c r="O69">
-        <v>2.3855535</v>
+        <v>2.325113999999999</v>
       </c>
       <c r="P69">
-        <v>13.5181365</v>
+        <v>13.175646</v>
       </c>
       <c r="Q69">
-        <v>30.6181365</v>
+        <v>30.275646</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3473584682515863</v>
+        <v>0.3562635786606277</v>
       </c>
       <c r="T69">
-        <v>1.844294052404801</v>
+        <v>1.89875659911631</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.589106066718007</v>
+        <v>1.565736859854507</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1660243451714009</v>
+        <v>0.1661653958197783</v>
       </c>
       <c r="C70">
-        <v>189.1983875017157</v>
+        <v>184.177841404839</v>
       </c>
       <c r="D70">
-        <v>463.8343875017158</v>
+        <v>463.290841404839</v>
       </c>
       <c r="E70">
-        <v>126.636</v>
+        <v>131.113</v>
       </c>
       <c r="F70">
-        <v>304.436</v>
+        <v>308.913</v>
       </c>
       <c r="G70">
         <v>29.8</v>
@@ -7021,28 +7021,28 @@
         <v>42.9</v>
       </c>
       <c r="M70">
-        <v>27.39924</v>
+        <v>27.80217</v>
       </c>
       <c r="N70">
-        <v>15.50076</v>
+        <v>15.09783</v>
       </c>
       <c r="O70">
-        <v>2.325113999999999</v>
+        <v>2.264674499999999</v>
       </c>
       <c r="P70">
-        <v>13.175646</v>
+        <v>12.8331555</v>
       </c>
       <c r="Q70">
-        <v>30.275646</v>
+        <v>29.9331555</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3562635786606277</v>
+        <v>0.3657432123218654</v>
       </c>
       <c r="T70">
-        <v>1.89875659911631</v>
+        <v>1.956732858518885</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.565736859854507</v>
+        <v>1.543045021305891</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1661653958197783</v>
+        <v>0.1663064464681556</v>
       </c>
       <c r="C71">
-        <v>184.177841404839</v>
+        <v>179.1585677300051</v>
       </c>
       <c r="D71">
-        <v>463.290841404839</v>
+        <v>462.7485677300052</v>
       </c>
       <c r="E71">
-        <v>131.113</v>
+        <v>135.59</v>
       </c>
       <c r="F71">
-        <v>308.913</v>
+        <v>313.39</v>
       </c>
       <c r="G71">
         <v>29.8</v>
@@ -7103,28 +7103,28 @@
         <v>42.9</v>
       </c>
       <c r="M71">
-        <v>27.80217</v>
+        <v>28.2051</v>
       </c>
       <c r="N71">
-        <v>15.09783</v>
+        <v>14.6949</v>
       </c>
       <c r="O71">
-        <v>2.264674499999999</v>
+        <v>2.204234999999999</v>
       </c>
       <c r="P71">
-        <v>12.8331555</v>
+        <v>12.490665</v>
       </c>
       <c r="Q71">
-        <v>29.9331555</v>
+        <v>29.590665</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3657432123218654</v>
+        <v>0.3758548215605189</v>
       </c>
       <c r="T71">
-        <v>1.956732858518885</v>
+        <v>2.018574201881631</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.543045021305891</v>
+        <v>1.521001521001521</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1663064464681556</v>
+        <v>0.2029371610799947</v>
       </c>
       <c r="C72">
-        <v>179.1585677300051</v>
+        <v>66.80886209466627</v>
       </c>
       <c r="D72">
-        <v>462.7485677300052</v>
+        <v>354.8758620946663</v>
       </c>
       <c r="E72">
-        <v>135.59</v>
+        <v>140.067</v>
       </c>
       <c r="F72">
-        <v>313.39</v>
+        <v>317.867</v>
       </c>
       <c r="G72">
         <v>29.8</v>
@@ -7185,45 +7185,45 @@
         <v>42.9</v>
       </c>
       <c r="M72">
-        <v>28.2051</v>
+        <v>46.66287560000001</v>
       </c>
       <c r="N72">
-        <v>14.6949</v>
+        <v>-3.762875600000008</v>
       </c>
       <c r="O72">
-        <v>2.204234999999999</v>
+        <v>-0.5644313400000012</v>
       </c>
       <c r="P72">
-        <v>12.490665</v>
+        <v>-3.198444260000007</v>
       </c>
       <c r="Q72">
-        <v>29.590665</v>
+        <v>13.90155574</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3758548215605189</v>
+        <v>0.3899400877705486</v>
       </c>
       <c r="T72">
-        <v>2.018574201881631</v>
+        <v>2.104717936621733</v>
       </c>
       <c r="U72">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.15</v>
+        <v>0.137904060074686</v>
       </c>
       <c r="W72">
-        <v>0.0765</v>
+        <v>0.1265556839810361</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.521001521001521</v>
+        <v>0.9193604004979066</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2029371610799947</v>
+        <v>0.2039471610799947</v>
       </c>
       <c r="C73">
-        <v>66.80886209466632</v>
+        <v>60.06546275959192</v>
       </c>
       <c r="D73">
-        <v>354.8758620946663</v>
+        <v>352.6094627595919</v>
       </c>
       <c r="E73">
-        <v>140.067</v>
+        <v>144.544</v>
       </c>
       <c r="F73">
-        <v>317.867</v>
+        <v>322.344</v>
       </c>
       <c r="G73">
         <v>29.8</v>
@@ -7267,37 +7267,37 @@
         <v>42.9</v>
       </c>
       <c r="M73">
-        <v>46.6628756</v>
+        <v>47.3200992</v>
       </c>
       <c r="N73">
-        <v>-3.762875600000001</v>
+        <v>-4.420099200000003</v>
       </c>
       <c r="O73">
-        <v>-0.5644313400000002</v>
+        <v>-0.6630148800000004</v>
       </c>
       <c r="P73">
-        <v>-3.198444260000001</v>
+        <v>-3.757084320000002</v>
       </c>
       <c r="Q73">
-        <v>13.90155574</v>
+        <v>13.34291568</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3899400877705484</v>
+        <v>0.4022308051909252</v>
       </c>
       <c r="T73">
-        <v>2.104717936621732</v>
+        <v>2.179886434358222</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.137904060074686</v>
+        <v>0.135988725906982</v>
       </c>
       <c r="W73">
-        <v>0.1265556839810361</v>
+        <v>0.126836855036855</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9193604004979067</v>
+        <v>0.9065915060465468</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2039471610799947</v>
+        <v>0.2049571610799947</v>
       </c>
       <c r="C74">
-        <v>60.06546275959192</v>
+        <v>53.35082824179489</v>
       </c>
       <c r="D74">
-        <v>352.6094627595919</v>
+        <v>350.3718282417948</v>
       </c>
       <c r="E74">
-        <v>144.544</v>
+        <v>149.021</v>
       </c>
       <c r="F74">
-        <v>322.344</v>
+        <v>326.821</v>
       </c>
       <c r="G74">
         <v>29.8</v>
@@ -7349,37 +7349,37 @@
         <v>42.9</v>
       </c>
       <c r="M74">
-        <v>47.3200992</v>
+        <v>47.9773228</v>
       </c>
       <c r="N74">
-        <v>-4.420099200000003</v>
+        <v>-5.077322800000005</v>
       </c>
       <c r="O74">
-        <v>-0.6630148800000004</v>
+        <v>-0.7615984200000007</v>
       </c>
       <c r="P74">
-        <v>-3.757084320000002</v>
+        <v>-4.315724380000004</v>
       </c>
       <c r="Q74">
-        <v>13.34291568</v>
+        <v>12.78427562</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4022308051909252</v>
+        <v>0.4154319461239224</v>
       </c>
       <c r="T74">
-        <v>2.179886434358222</v>
+        <v>2.260622968964082</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.135988725906982</v>
+        <v>0.1341258666479823</v>
       </c>
       <c r="W74">
-        <v>0.126836855036855</v>
+        <v>0.1271103227760762</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9065915060465468</v>
+        <v>0.8941724443198817</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2049571610799947</v>
+        <v>0.2059671610799947</v>
       </c>
       <c r="C75">
-        <v>53.35082824179489</v>
+        <v>46.66441437606818</v>
       </c>
       <c r="D75">
-        <v>350.3718282417948</v>
+        <v>348.1624143760682</v>
       </c>
       <c r="E75">
-        <v>149.021</v>
+        <v>153.498</v>
       </c>
       <c r="F75">
-        <v>326.821</v>
+        <v>331.298</v>
       </c>
       <c r="G75">
         <v>29.8</v>
@@ -7431,37 +7431,37 @@
         <v>42.9</v>
       </c>
       <c r="M75">
-        <v>47.9773228</v>
+        <v>48.6345464</v>
       </c>
       <c r="N75">
-        <v>-5.077322800000005</v>
+        <v>-5.734546400000006</v>
       </c>
       <c r="O75">
-        <v>-0.7615984200000007</v>
+        <v>-0.8601819600000009</v>
       </c>
       <c r="P75">
-        <v>-4.315724380000004</v>
+        <v>-4.874364440000005</v>
       </c>
       <c r="Q75">
-        <v>12.78427562</v>
+        <v>12.22563556</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4154319461239224</v>
+        <v>0.429648559436381</v>
       </c>
       <c r="T75">
-        <v>2.260622968964082</v>
+        <v>2.347570006231932</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1341258666479823</v>
+        <v>0.132313354936523</v>
       </c>
       <c r="W75">
-        <v>0.1271103227760762</v>
+        <v>0.1273763994953184</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8941724443198817</v>
+        <v>0.8820890329101536</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2059671610799947</v>
+        <v>0.2069771610799947</v>
       </c>
       <c r="C76">
-        <v>46.66441437606818</v>
+        <v>40.00569063702488</v>
       </c>
       <c r="D76">
-        <v>348.1624143760682</v>
+        <v>345.9806906370248</v>
       </c>
       <c r="E76">
-        <v>153.498</v>
+        <v>157.975</v>
       </c>
       <c r="F76">
-        <v>331.298</v>
+        <v>335.775</v>
       </c>
       <c r="G76">
         <v>29.8</v>
@@ -7513,37 +7513,37 @@
         <v>42.9</v>
       </c>
       <c r="M76">
-        <v>48.6345464</v>
+        <v>49.29177</v>
       </c>
       <c r="N76">
-        <v>-5.734546400000006</v>
+        <v>-6.391770000000001</v>
       </c>
       <c r="O76">
-        <v>-0.8601819600000009</v>
+        <v>-0.9587655000000002</v>
       </c>
       <c r="P76">
-        <v>-4.874364440000005</v>
+        <v>-5.433004500000001</v>
       </c>
       <c r="Q76">
-        <v>12.22563556</v>
+        <v>11.6669955</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.429648559436381</v>
+        <v>0.4450025018138362</v>
       </c>
       <c r="T76">
-        <v>2.347570006231932</v>
+        <v>2.441472806481209</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.132313354936523</v>
+        <v>0.1305491768707027</v>
       </c>
       <c r="W76">
-        <v>0.1273763994953184</v>
+        <v>0.1276353808353808</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8820890329101536</v>
+        <v>0.870327845804685</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2069771610799947</v>
+        <v>0.2079871610799947</v>
       </c>
       <c r="C77">
-        <v>40.00569063702488</v>
+        <v>33.37413971439634</v>
       </c>
       <c r="D77">
-        <v>345.9806906370248</v>
+        <v>343.8261397143963</v>
       </c>
       <c r="E77">
-        <v>157.975</v>
+        <v>162.452</v>
       </c>
       <c r="F77">
-        <v>335.775</v>
+        <v>340.252</v>
       </c>
       <c r="G77">
         <v>29.8</v>
@@ -7595,37 +7595,37 @@
         <v>42.9</v>
       </c>
       <c r="M77">
-        <v>49.29177</v>
+        <v>49.94899360000001</v>
       </c>
       <c r="N77">
-        <v>-6.391770000000001</v>
+        <v>-7.04899360000001</v>
       </c>
       <c r="O77">
-        <v>-0.9587655000000002</v>
+        <v>-1.057349040000001</v>
       </c>
       <c r="P77">
-        <v>-5.433004500000001</v>
+        <v>-5.991644560000008</v>
       </c>
       <c r="Q77">
-        <v>11.6669955</v>
+        <v>11.10835543999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4450025018138362</v>
+        <v>0.4616359393894127</v>
       </c>
       <c r="T77">
-        <v>2.441472806481209</v>
+        <v>2.543200840084593</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1305491768707027</v>
+        <v>0.1288314245434566</v>
       </c>
       <c r="W77">
-        <v>0.1276353808353808</v>
+        <v>0.1278875468770206</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.870327845804685</v>
+        <v>0.8588761636230443</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2079871610799947</v>
+        <v>0.2089971610799947</v>
       </c>
       <c r="C78">
-        <v>33.37413971439634</v>
+        <v>26.769257104102</v>
       </c>
       <c r="D78">
-        <v>343.8261397143963</v>
+        <v>341.698257104102</v>
       </c>
       <c r="E78">
-        <v>162.452</v>
+        <v>166.929</v>
       </c>
       <c r="F78">
-        <v>340.252</v>
+        <v>344.729</v>
       </c>
       <c r="G78">
         <v>29.8</v>
@@ -7677,37 +7677,37 @@
         <v>42.9</v>
       </c>
       <c r="M78">
-        <v>49.94899360000001</v>
+        <v>50.6062172</v>
       </c>
       <c r="N78">
-        <v>-7.04899360000001</v>
+        <v>-7.706217200000005</v>
       </c>
       <c r="O78">
-        <v>-1.057349040000001</v>
+        <v>-1.155932580000001</v>
       </c>
       <c r="P78">
-        <v>-5.991644560000008</v>
+        <v>-6.550284620000004</v>
       </c>
       <c r="Q78">
-        <v>11.10835543999999</v>
+        <v>10.54971538</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4616359393894127</v>
+        <v>0.4797157628411264</v>
       </c>
       <c r="T78">
-        <v>2.543200840084593</v>
+        <v>2.653774789653488</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1288314245434566</v>
+        <v>0.1271582891597754</v>
       </c>
       <c r="W78">
-        <v>0.1278875468770206</v>
+        <v>0.128133163151345</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8588761636230443</v>
+        <v>0.847721927731836</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2089971610799947</v>
+        <v>0.2100071610799947</v>
       </c>
       <c r="C79">
-        <v>26.769257104102</v>
+        <v>20.19055071440914</v>
       </c>
       <c r="D79">
-        <v>341.698257104102</v>
+        <v>339.5965507144091</v>
       </c>
       <c r="E79">
-        <v>166.929</v>
+        <v>171.406</v>
       </c>
       <c r="F79">
-        <v>344.729</v>
+        <v>349.206</v>
       </c>
       <c r="G79">
         <v>29.8</v>
@@ -7759,37 +7759,37 @@
         <v>42.9</v>
       </c>
       <c r="M79">
-        <v>50.6062172</v>
+        <v>51.26344080000001</v>
       </c>
       <c r="N79">
-        <v>-7.706217200000005</v>
+        <v>-8.363440800000006</v>
       </c>
       <c r="O79">
-        <v>-1.155932580000001</v>
+        <v>-1.254516120000001</v>
       </c>
       <c r="P79">
-        <v>-6.550284620000004</v>
+        <v>-7.108924680000006</v>
       </c>
       <c r="Q79">
-        <v>10.54971538</v>
+        <v>9.991075319999997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4797157628411264</v>
+        <v>0.4994392066066321</v>
       </c>
       <c r="T79">
-        <v>2.653774789653488</v>
+        <v>2.77440091645592</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1271582891597754</v>
+        <v>0.125528054683368</v>
       </c>
       <c r="W79">
-        <v>0.128133163151345</v>
+        <v>0.1283724815724816</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.847721927731836</v>
+        <v>0.8368536978891201</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2100071610799947</v>
+        <v>0.2110171610799947</v>
       </c>
       <c r="C80">
-        <v>20.19055071440914</v>
+        <v>13.63754048654016</v>
       </c>
       <c r="D80">
-        <v>339.5965507144091</v>
+        <v>337.5205404865401</v>
       </c>
       <c r="E80">
-        <v>171.406</v>
+        <v>175.883</v>
       </c>
       <c r="F80">
-        <v>349.206</v>
+        <v>353.683</v>
       </c>
       <c r="G80">
         <v>29.8</v>
@@ -7841,37 +7841,37 @@
         <v>42.9</v>
       </c>
       <c r="M80">
-        <v>51.26344080000001</v>
+        <v>51.92066440000001</v>
       </c>
       <c r="N80">
-        <v>-8.363440800000006</v>
+        <v>-9.020664400000008</v>
       </c>
       <c r="O80">
-        <v>-1.254516120000001</v>
+        <v>-1.353099660000001</v>
       </c>
       <c r="P80">
-        <v>-7.108924680000006</v>
+        <v>-7.667564740000007</v>
       </c>
       <c r="Q80">
-        <v>9.991075319999997</v>
+        <v>9.432435259999995</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4994392066066321</v>
+        <v>0.5210410735879003</v>
       </c>
       <c r="T80">
-        <v>2.77440091645592</v>
+        <v>2.906515245810964</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.125528054683368</v>
+        <v>0.123939091965857</v>
       </c>
       <c r="W80">
-        <v>0.1283724815724816</v>
+        <v>0.1286057412994122</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8368536978891201</v>
+        <v>0.8262606131057135</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2110171610799947</v>
+        <v>0.2120271610799947</v>
       </c>
       <c r="C81">
-        <v>13.63754048654016</v>
+        <v>7.109758029109116</v>
       </c>
       <c r="D81">
-        <v>337.5205404865401</v>
+        <v>335.4697580291091</v>
       </c>
       <c r="E81">
-        <v>175.883</v>
+        <v>180.36</v>
       </c>
       <c r="F81">
-        <v>353.683</v>
+        <v>358.16</v>
       </c>
       <c r="G81">
         <v>29.8</v>
@@ -7923,37 +7923,37 @@
         <v>42.9</v>
       </c>
       <c r="M81">
-        <v>51.92066440000001</v>
+        <v>52.57788800000001</v>
       </c>
       <c r="N81">
-        <v>-9.020664400000008</v>
+        <v>-9.67788800000001</v>
       </c>
       <c r="O81">
-        <v>-1.353099660000001</v>
+        <v>-1.451683200000002</v>
       </c>
       <c r="P81">
-        <v>-7.667564740000007</v>
+        <v>-8.226204800000009</v>
       </c>
       <c r="Q81">
-        <v>9.432435259999995</v>
+        <v>8.873795199999993</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5210410735879003</v>
+        <v>0.5448031272672954</v>
       </c>
       <c r="T81">
-        <v>2.906515245810964</v>
+        <v>3.051841008101512</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.123939091965857</v>
+        <v>0.1223898533162838</v>
       </c>
       <c r="W81">
-        <v>0.1286057412994122</v>
+        <v>0.1288331695331695</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8262606131057135</v>
+        <v>0.815932355441892</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2120271610799947</v>
+        <v>0.2130371610799947</v>
       </c>
       <c r="C82">
-        <v>7.109758029109116</v>
+        <v>0.606746265806521</v>
       </c>
       <c r="D82">
-        <v>335.4697580291091</v>
+        <v>333.4437462658065</v>
       </c>
       <c r="E82">
-        <v>180.36</v>
+        <v>184.837</v>
       </c>
       <c r="F82">
-        <v>358.16</v>
+        <v>362.637</v>
       </c>
       <c r="G82">
         <v>29.8</v>
@@ -8005,37 +8005,37 @@
         <v>42.9</v>
       </c>
       <c r="M82">
-        <v>52.57788800000001</v>
+        <v>53.2351116</v>
       </c>
       <c r="N82">
-        <v>-9.67788800000001</v>
+        <v>-10.3351116</v>
       </c>
       <c r="O82">
-        <v>-1.451683200000002</v>
+        <v>-1.550266740000001</v>
       </c>
       <c r="P82">
-        <v>-8.226204800000009</v>
+        <v>-8.784844860000003</v>
       </c>
       <c r="Q82">
-        <v>8.873795199999993</v>
+        <v>8.315155139999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5448031272672954</v>
+        <v>0.5710664497550478</v>
       </c>
       <c r="T82">
-        <v>3.051841008101512</v>
+        <v>3.212464219054223</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1223898533162838</v>
+        <v>0.1208788674728729</v>
       </c>
       <c r="W82">
-        <v>0.1288331695331695</v>
+        <v>0.1290549822549823</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.815932355441892</v>
+        <v>0.8058591164858194</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2130371610799947</v>
+        <v>0.2612402232509462</v>
       </c>
       <c r="C83">
-        <v>0.606746265806521</v>
+        <v>-78.47567972766598</v>
       </c>
       <c r="D83">
-        <v>333.4437462658065</v>
+        <v>258.838320272334</v>
       </c>
       <c r="E83">
-        <v>184.837</v>
+        <v>189.314</v>
       </c>
       <c r="F83">
-        <v>362.637</v>
+        <v>367.114</v>
       </c>
       <c r="G83">
         <v>29.8</v>
@@ -8087,45 +8087,45 @@
         <v>42.9</v>
       </c>
       <c r="M83">
-        <v>53.2351116</v>
+        <v>73.71649120000001</v>
       </c>
       <c r="N83">
-        <v>-10.3351116</v>
+        <v>-30.81649120000001</v>
       </c>
       <c r="O83">
-        <v>-1.550266740000001</v>
+        <v>-4.622473680000001</v>
       </c>
       <c r="P83">
-        <v>-8.784844860000003</v>
+        <v>-26.19401752000001</v>
       </c>
       <c r="Q83">
-        <v>8.315155139999998</v>
+        <v>-9.094017520000005</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5710664497550478</v>
+        <v>0.6164315979133923</v>
       </c>
       <c r="T83">
-        <v>3.212464219054223</v>
+        <v>3.48991181792283</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1208788674728729</v>
+        <v>0.08729389984855924</v>
       </c>
       <c r="W83">
-        <v>0.1290549822549823</v>
+        <v>0.1832713849104093</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8058591164858194</v>
+        <v>0.5819593323237283</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2612402232509462</v>
+        <v>0.2627902232509462</v>
       </c>
       <c r="C84">
-        <v>-78.47567972766598</v>
+        <v>-84.80160817435512</v>
       </c>
       <c r="D84">
-        <v>258.838320272334</v>
+        <v>256.9893918256449</v>
       </c>
       <c r="E84">
-        <v>189.314</v>
+        <v>193.791</v>
       </c>
       <c r="F84">
-        <v>367.114</v>
+        <v>371.591</v>
       </c>
       <c r="G84">
         <v>29.8</v>
@@ -8169,37 +8169,37 @@
         <v>42.9</v>
       </c>
       <c r="M84">
-        <v>73.71649120000001</v>
+        <v>74.61547280000001</v>
       </c>
       <c r="N84">
-        <v>-30.81649120000001</v>
+        <v>-31.71547280000001</v>
       </c>
       <c r="O84">
-        <v>-4.622473680000001</v>
+        <v>-4.757320920000001</v>
       </c>
       <c r="P84">
-        <v>-26.19401752000001</v>
+        <v>-26.95815188000001</v>
       </c>
       <c r="Q84">
-        <v>-9.094017520000005</v>
+        <v>-9.858151880000005</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6164315979133923</v>
+        <v>0.6499981624965331</v>
       </c>
       <c r="T84">
-        <v>3.48991181792283</v>
+        <v>3.695200748388879</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08729389984855924</v>
+        <v>0.08624216611544407</v>
       </c>
       <c r="W84">
-        <v>0.1832713849104093</v>
+        <v>0.1834825730440188</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5819593323237283</v>
+        <v>0.5749477741029605</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2627902232509462</v>
+        <v>0.2643402232509462</v>
       </c>
       <c r="C85">
-        <v>-84.80160817435512</v>
+        <v>-91.10130951237096</v>
       </c>
       <c r="D85">
-        <v>256.9893918256449</v>
+        <v>255.1666904876291</v>
       </c>
       <c r="E85">
-        <v>193.791</v>
+        <v>198.268</v>
       </c>
       <c r="F85">
-        <v>371.591</v>
+        <v>376.068</v>
       </c>
       <c r="G85">
         <v>29.8</v>
@@ -8251,37 +8251,37 @@
         <v>42.9</v>
       </c>
       <c r="M85">
-        <v>74.61547280000001</v>
+        <v>75.51445440000001</v>
       </c>
       <c r="N85">
-        <v>-31.71547280000001</v>
+        <v>-32.61445440000001</v>
       </c>
       <c r="O85">
-        <v>-4.757320920000001</v>
+        <v>-4.892168160000001</v>
       </c>
       <c r="P85">
-        <v>-26.95815188000001</v>
+        <v>-27.72228624000001</v>
       </c>
       <c r="Q85">
-        <v>-9.858151880000005</v>
+        <v>-10.62228624</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6499981624965331</v>
+        <v>0.6877605476525667</v>
       </c>
       <c r="T85">
-        <v>3.695200748388879</v>
+        <v>3.926150795163185</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08624216611544407</v>
+        <v>0.08521547366168879</v>
       </c>
       <c r="W85">
-        <v>0.1834825730440188</v>
+        <v>0.1836887328887329</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5749477741029605</v>
+        <v>0.568103157744592</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2643402232509462</v>
+        <v>0.2658902232509462</v>
       </c>
       <c r="C86">
-        <v>-91.10130951237079</v>
+        <v>-97.37533786017201</v>
       </c>
       <c r="D86">
-        <v>255.1666904876292</v>
+        <v>253.369662139828</v>
       </c>
       <c r="E86">
-        <v>198.268</v>
+        <v>202.7449999999999</v>
       </c>
       <c r="F86">
-        <v>376.068</v>
+        <v>380.545</v>
       </c>
       <c r="G86">
         <v>29.8</v>
@@ -8333,37 +8333,37 @@
         <v>42.9</v>
       </c>
       <c r="M86">
-        <v>75.51445440000001</v>
+        <v>76.41343599999999</v>
       </c>
       <c r="N86">
-        <v>-32.61445440000001</v>
+        <v>-33.51343599999999</v>
       </c>
       <c r="O86">
-        <v>-4.892168160000001</v>
+        <v>-5.027015399999999</v>
       </c>
       <c r="P86">
-        <v>-27.72228624000001</v>
+        <v>-28.48642059999999</v>
       </c>
       <c r="Q86">
-        <v>-10.62228624</v>
+        <v>-11.38642059999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6877605476525661</v>
+        <v>0.7305579174960706</v>
       </c>
       <c r="T86">
-        <v>3.926150795163182</v>
+        <v>4.187894181507394</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.08521547366168879</v>
+        <v>0.08421293867743364</v>
       </c>
       <c r="W86">
-        <v>0.1836887328887329</v>
+        <v>0.1838900419135713</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.568103157744592</v>
+        <v>0.561419591182891</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2658902232509462</v>
+        <v>0.2674402232509462</v>
       </c>
       <c r="C87">
-        <v>-97.37533786017201</v>
+        <v>-103.6242318357167</v>
       </c>
       <c r="D87">
-        <v>253.369662139828</v>
+        <v>251.5977681642833</v>
       </c>
       <c r="E87">
-        <v>202.7449999999999</v>
+        <v>207.222</v>
       </c>
       <c r="F87">
-        <v>380.545</v>
+        <v>385.022</v>
       </c>
       <c r="G87">
         <v>29.8</v>
@@ -8415,37 +8415,37 @@
         <v>42.9</v>
       </c>
       <c r="M87">
-        <v>76.41343599999999</v>
+        <v>77.3124176</v>
       </c>
       <c r="N87">
-        <v>-33.51343599999999</v>
+        <v>-34.4124176</v>
       </c>
       <c r="O87">
-        <v>-5.027015399999999</v>
+        <v>-5.161862640000001</v>
       </c>
       <c r="P87">
-        <v>-28.48642059999999</v>
+        <v>-29.25055496</v>
       </c>
       <c r="Q87">
-        <v>-11.38642059999999</v>
+        <v>-12.15055496</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7305579174960706</v>
+        <v>0.7794691973172185</v>
       </c>
       <c r="T87">
-        <v>4.187894181507394</v>
+        <v>4.487029480186494</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08421293867743364</v>
+        <v>0.08323371846025417</v>
       </c>
       <c r="W87">
-        <v>0.1838900419135713</v>
+        <v>0.184086669333181</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.561419591182891</v>
+        <v>0.5548914564016945</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2674402232509462</v>
+        <v>0.2689902232509462</v>
       </c>
       <c r="C88">
-        <v>-103.6242318357167</v>
+        <v>-109.8485150946978</v>
       </c>
       <c r="D88">
-        <v>251.5977681642833</v>
+        <v>249.8504849053022</v>
       </c>
       <c r="E88">
-        <v>207.222</v>
+        <v>211.699</v>
       </c>
       <c r="F88">
-        <v>385.022</v>
+        <v>389.499</v>
       </c>
       <c r="G88">
         <v>29.8</v>
@@ -8497,37 +8497,37 @@
         <v>42.9</v>
       </c>
       <c r="M88">
-        <v>77.3124176</v>
+        <v>78.2113992</v>
       </c>
       <c r="N88">
-        <v>-34.4124176</v>
+        <v>-35.3113992</v>
       </c>
       <c r="O88">
-        <v>-5.161862640000001</v>
+        <v>-5.296709880000001</v>
       </c>
       <c r="P88">
-        <v>-29.25055496</v>
+        <v>-30.01468932</v>
       </c>
       <c r="Q88">
-        <v>-12.15055496</v>
+        <v>-12.91468932</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7794691973172185</v>
+        <v>0.835905289418543</v>
       </c>
       <c r="T88">
-        <v>4.487029480186494</v>
+        <v>4.832185594046994</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08323371846025417</v>
+        <v>0.08227700905266504</v>
       </c>
       <c r="W88">
-        <v>0.184086669333181</v>
+        <v>0.1842787765822249</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5548914564016945</v>
+        <v>0.5485133936844336</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2689902232509462</v>
+        <v>0.2705402232509463</v>
       </c>
       <c r="C89">
-        <v>-109.8485150946978</v>
+        <v>-116.0486968465056</v>
       </c>
       <c r="D89">
-        <v>249.8504849053022</v>
+        <v>248.1273031534944</v>
       </c>
       <c r="E89">
-        <v>211.699</v>
+        <v>216.176</v>
       </c>
       <c r="F89">
-        <v>389.499</v>
+        <v>393.976</v>
       </c>
       <c r="G89">
         <v>29.8</v>
@@ -8579,37 +8579,37 @@
         <v>42.9</v>
       </c>
       <c r="M89">
-        <v>78.2113992</v>
+        <v>79.1103808</v>
       </c>
       <c r="N89">
-        <v>-35.3113992</v>
+        <v>-36.2103808</v>
       </c>
       <c r="O89">
-        <v>-5.296709880000001</v>
+        <v>-5.43155712</v>
       </c>
       <c r="P89">
-        <v>-30.01468932</v>
+        <v>-30.77882368</v>
       </c>
       <c r="Q89">
-        <v>-12.91468932</v>
+        <v>-13.67882368</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.835905289418543</v>
+        <v>0.9017473968700884</v>
       </c>
       <c r="T89">
-        <v>4.832185594046994</v>
+        <v>5.234867726884244</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08227700905266504</v>
+        <v>0.08134204304070294</v>
       </c>
       <c r="W89">
-        <v>0.1842787765822249</v>
+        <v>0.1844665177574269</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5485133936844336</v>
+        <v>0.5422802869380197</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2705402232509463</v>
+        <v>0.2720902232509462</v>
       </c>
       <c r="C90">
-        <v>-116.0486968465056</v>
+        <v>-122.225272348985</v>
       </c>
       <c r="D90">
-        <v>248.1273031534944</v>
+        <v>246.427727651015</v>
       </c>
       <c r="E90">
-        <v>216.176</v>
+        <v>220.653</v>
       </c>
       <c r="F90">
-        <v>393.976</v>
+        <v>398.453</v>
       </c>
       <c r="G90">
         <v>29.8</v>
@@ -8661,37 +8661,37 @@
         <v>42.9</v>
       </c>
       <c r="M90">
-        <v>79.1103808</v>
+        <v>80.0093624</v>
       </c>
       <c r="N90">
-        <v>-36.2103808</v>
+        <v>-37.1093624</v>
       </c>
       <c r="O90">
-        <v>-5.43155712</v>
+        <v>-5.56640436</v>
       </c>
       <c r="P90">
-        <v>-30.77882368</v>
+        <v>-31.54295804</v>
       </c>
       <c r="Q90">
-        <v>-13.67882368</v>
+        <v>-14.44295804</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9017473968700884</v>
+        <v>0.979560796585551</v>
       </c>
       <c r="T90">
-        <v>5.234867726884244</v>
+        <v>5.710764792964629</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08134204304070294</v>
+        <v>0.08042808750091976</v>
       </c>
       <c r="W90">
-        <v>0.1844665177574269</v>
+        <v>0.1846500400298153</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5422802869380197</v>
+        <v>0.5361872500061318</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2720902232509462</v>
+        <v>0.2736402232509463</v>
       </c>
       <c r="C91">
-        <v>-122.225272348985</v>
+        <v>-128.3787233829992</v>
       </c>
       <c r="D91">
-        <v>246.427727651015</v>
+        <v>244.7512766170008</v>
       </c>
       <c r="E91">
-        <v>220.653</v>
+        <v>225.13</v>
       </c>
       <c r="F91">
-        <v>398.453</v>
+        <v>402.93</v>
       </c>
       <c r="G91">
         <v>29.8</v>
@@ -8743,37 +8743,37 @@
         <v>42.9</v>
       </c>
       <c r="M91">
-        <v>80.0093624</v>
+        <v>80.908344</v>
       </c>
       <c r="N91">
-        <v>-37.1093624</v>
+        <v>-38.008344</v>
       </c>
       <c r="O91">
-        <v>-5.56640436</v>
+        <v>-5.7012516</v>
       </c>
       <c r="P91">
-        <v>-31.54295804</v>
+        <v>-32.3070924</v>
       </c>
       <c r="Q91">
-        <v>-14.44295804</v>
+        <v>-15.2070924</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.979560796585551</v>
+        <v>1.072936876244106</v>
       </c>
       <c r="T91">
-        <v>5.710764792964629</v>
+        <v>6.281841272261093</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08042808750091976</v>
+        <v>0.07953444208424287</v>
       </c>
       <c r="W91">
-        <v>0.1846500400298153</v>
+        <v>0.184829484029484</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5361872500061318</v>
+        <v>0.5302296138949525</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2736402232509463</v>
+        <v>0.2751902232509462</v>
       </c>
       <c r="C92">
-        <v>-128.3787233829992</v>
+        <v>-134.5095187077516</v>
       </c>
       <c r="D92">
-        <v>244.7512766170008</v>
+        <v>243.0974812922483</v>
       </c>
       <c r="E92">
-        <v>225.13</v>
+        <v>229.607</v>
       </c>
       <c r="F92">
-        <v>402.93</v>
+        <v>407.407</v>
       </c>
       <c r="G92">
         <v>29.8</v>
@@ -8825,37 +8825,37 @@
         <v>42.9</v>
       </c>
       <c r="M92">
-        <v>80.908344</v>
+        <v>81.8073256</v>
       </c>
       <c r="N92">
-        <v>-38.008344</v>
+        <v>-38.9073256</v>
       </c>
       <c r="O92">
-        <v>-5.7012516</v>
+        <v>-5.83609884</v>
       </c>
       <c r="P92">
-        <v>-32.3070924</v>
+        <v>-33.07122676</v>
       </c>
       <c r="Q92">
-        <v>-15.2070924</v>
+        <v>-15.97122676</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.072936876244106</v>
+        <v>1.187063195826785</v>
       </c>
       <c r="T92">
-        <v>6.281841272261093</v>
+        <v>6.979823635845659</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07953444208424287</v>
+        <v>0.07866043722617427</v>
       </c>
       <c r="W92">
-        <v>0.184829484029484</v>
+        <v>0.1850049842049842</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5302296138949525</v>
+        <v>0.5244029148411619</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2751902232509462</v>
+        <v>0.2767402232509463</v>
       </c>
       <c r="C93">
-        <v>-134.5095187077516</v>
+        <v>-140.6181144977738</v>
       </c>
       <c r="D93">
-        <v>243.0974812922483</v>
+        <v>241.4658855022263</v>
       </c>
       <c r="E93">
-        <v>229.607</v>
+        <v>234.084</v>
       </c>
       <c r="F93">
-        <v>407.407</v>
+        <v>411.884</v>
       </c>
       <c r="G93">
         <v>29.8</v>
@@ -8907,37 +8907,37 @@
         <v>42.9</v>
       </c>
       <c r="M93">
-        <v>81.8073256</v>
+        <v>82.70630720000001</v>
       </c>
       <c r="N93">
-        <v>-38.9073256</v>
+        <v>-39.80630720000001</v>
       </c>
       <c r="O93">
-        <v>-5.83609884</v>
+        <v>-5.970946080000002</v>
       </c>
       <c r="P93">
-        <v>-33.07122676</v>
+        <v>-33.83536112000001</v>
       </c>
       <c r="Q93">
-        <v>-15.97122676</v>
+        <v>-16.73536112000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.187063195826785</v>
+        <v>1.329721095305133</v>
       </c>
       <c r="T93">
-        <v>6.979823635845659</v>
+        <v>7.85230159032637</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07866043722617427</v>
+        <v>0.07780543247371584</v>
       </c>
       <c r="W93">
-        <v>0.1850049842049842</v>
+        <v>0.1851766691592779</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5244029148411619</v>
+        <v>0.5187028831581056</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2767402232509463</v>
+        <v>0.2782902232509463</v>
       </c>
       <c r="C94">
-        <v>-140.6181144977738</v>
+        <v>-146.7049547624306</v>
       </c>
       <c r="D94">
-        <v>241.4658855022263</v>
+        <v>239.8560452375693</v>
       </c>
       <c r="E94">
-        <v>234.084</v>
+        <v>238.561</v>
       </c>
       <c r="F94">
-        <v>411.884</v>
+        <v>416.361</v>
       </c>
       <c r="G94">
         <v>29.8</v>
@@ -8989,37 +8989,37 @@
         <v>42.9</v>
       </c>
       <c r="M94">
-        <v>82.70630720000001</v>
+        <v>83.6052888</v>
       </c>
       <c r="N94">
-        <v>-39.80630720000001</v>
+        <v>-40.7052888</v>
       </c>
       <c r="O94">
-        <v>-5.970946080000002</v>
+        <v>-6.105793319999999</v>
       </c>
       <c r="P94">
-        <v>-33.83536112000001</v>
+        <v>-34.59949548</v>
       </c>
       <c r="Q94">
-        <v>-16.73536112000001</v>
+        <v>-17.49949548</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.329721095305133</v>
+        <v>1.513138394634438</v>
       </c>
       <c r="T94">
-        <v>7.85230159032637</v>
+        <v>8.974058960372995</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07780543247371584</v>
+        <v>0.07696881492023504</v>
       </c>
       <c r="W94">
-        <v>0.1851766691592779</v>
+        <v>0.1853446619640168</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5187028831581056</v>
+        <v>0.513125432801567</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2782902232509463</v>
+        <v>0.2798402232509463</v>
       </c>
       <c r="C95">
-        <v>-146.7049547624306</v>
+        <v>-152.7704717487591</v>
       </c>
       <c r="D95">
-        <v>239.8560452375693</v>
+        <v>238.2675282512409</v>
       </c>
       <c r="E95">
-        <v>238.561</v>
+        <v>243.038</v>
       </c>
       <c r="F95">
-        <v>416.361</v>
+        <v>420.838</v>
       </c>
       <c r="G95">
         <v>29.8</v>
@@ -9071,37 +9071,37 @@
         <v>42.9</v>
       </c>
       <c r="M95">
-        <v>83.6052888</v>
+        <v>84.50427040000001</v>
       </c>
       <c r="N95">
-        <v>-40.7052888</v>
+        <v>-41.60427040000001</v>
       </c>
       <c r="O95">
-        <v>-6.105793319999999</v>
+        <v>-6.240640560000002</v>
       </c>
       <c r="P95">
-        <v>-34.59949548</v>
+        <v>-35.36362984000001</v>
       </c>
       <c r="Q95">
-        <v>-17.49949548</v>
+        <v>-18.26362984000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.513138394634438</v>
+        <v>1.757694793740178</v>
       </c>
       <c r="T95">
-        <v>8.974058960372995</v>
+        <v>10.4697354537685</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07696881492023504</v>
+        <v>0.07614999774023253</v>
       </c>
       <c r="W95">
-        <v>0.1853446619640168</v>
+        <v>0.1855090804537613</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.513125432801567</v>
+        <v>0.5076666516015502</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2798402232509463</v>
+        <v>0.2813902232509463</v>
       </c>
       <c r="C96">
-        <v>-152.7704717487591</v>
+        <v>-158.8150863284016</v>
       </c>
       <c r="D96">
-        <v>238.2675282512409</v>
+        <v>236.6999136715984</v>
       </c>
       <c r="E96">
-        <v>243.038</v>
+        <v>247.515</v>
       </c>
       <c r="F96">
-        <v>420.838</v>
+        <v>425.315</v>
       </c>
       <c r="G96">
         <v>29.8</v>
@@ -9153,37 +9153,37 @@
         <v>42.9</v>
       </c>
       <c r="M96">
-        <v>84.50427040000001</v>
+        <v>85.40325200000001</v>
       </c>
       <c r="N96">
-        <v>-41.60427040000001</v>
+        <v>-42.50325200000001</v>
       </c>
       <c r="O96">
-        <v>-6.240640560000002</v>
+        <v>-6.375487800000001</v>
       </c>
       <c r="P96">
-        <v>-35.36362984000001</v>
+        <v>-36.12776420000001</v>
       </c>
       <c r="Q96">
-        <v>-18.26362984000001</v>
+        <v>-19.02776420000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.757694793740178</v>
+        <v>2.100073752488215</v>
       </c>
       <c r="T96">
-        <v>10.4697354537685</v>
+        <v>12.5636825445222</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07614999774023253</v>
+        <v>0.07534841881665114</v>
       </c>
       <c r="W96">
-        <v>0.1855090804537613</v>
+        <v>0.1856700375016165</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5076666516015502</v>
+        <v>0.5023227921110076</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2813902232509463</v>
+        <v>0.3177156790228142</v>
       </c>
       <c r="C97">
-        <v>-158.8150863284016</v>
+        <v>-194.9130368972771</v>
       </c>
       <c r="D97">
-        <v>236.6999136715984</v>
+        <v>205.0789631027229</v>
       </c>
       <c r="E97">
-        <v>247.515</v>
+        <v>251.992</v>
       </c>
       <c r="F97">
-        <v>425.315</v>
+        <v>429.792</v>
       </c>
       <c r="G97">
         <v>29.8</v>
@@ -9235,45 +9235,45 @@
         <v>42.9</v>
       </c>
       <c r="M97">
-        <v>85.40325200000001</v>
+        <v>101.3449536</v>
       </c>
       <c r="N97">
-        <v>-42.50325200000001</v>
+        <v>-58.44495360000001</v>
       </c>
       <c r="O97">
-        <v>-6.375487800000001</v>
+        <v>-8.766743040000001</v>
       </c>
       <c r="P97">
-        <v>-36.12776420000001</v>
+        <v>-49.67821056000001</v>
       </c>
       <c r="Q97">
-        <v>-19.02776420000001</v>
+        <v>-32.57821056000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.100073752488215</v>
+        <v>2.643028584906968</v>
       </c>
       <c r="T97">
-        <v>12.5636825445222</v>
+        <v>15.88432671001426</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07534841881665114</v>
+        <v>0.06349600815249669</v>
       </c>
       <c r="W97">
-        <v>0.1856700375016165</v>
+        <v>0.2208276412776413</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5023227921110076</v>
+        <v>0.4233067210166446</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3177156790228142</v>
+        <v>0.3196156790228142</v>
       </c>
       <c r="C98">
-        <v>-194.913036897277</v>
+        <v>-200.8130745819186</v>
       </c>
       <c r="D98">
-        <v>205.078963102723</v>
+        <v>203.6559254180814</v>
       </c>
       <c r="E98">
-        <v>251.992</v>
+        <v>256.469</v>
       </c>
       <c r="F98">
-        <v>429.792</v>
+        <v>434.269</v>
       </c>
       <c r="G98">
         <v>29.8</v>
@@ -9317,37 +9317,37 @@
         <v>42.9</v>
       </c>
       <c r="M98">
-        <v>101.3449536</v>
+        <v>102.4006302</v>
       </c>
       <c r="N98">
-        <v>-58.4449536</v>
+        <v>-59.50063020000001</v>
       </c>
       <c r="O98">
-        <v>-8.76674304</v>
+        <v>-8.925094530000001</v>
       </c>
       <c r="P98">
-        <v>-49.67821056</v>
+        <v>-50.57553567000001</v>
       </c>
       <c r="Q98">
-        <v>-32.57821056</v>
+        <v>-33.47553567000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.643028584906962</v>
+        <v>3.508771446542616</v>
       </c>
       <c r="T98">
-        <v>15.88432671001422</v>
+        <v>21.17910228001896</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0634960081524967</v>
+        <v>0.062841410130306</v>
       </c>
       <c r="W98">
-        <v>0.2208276412776413</v>
+        <v>0.2209819954912739</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4233067210166447</v>
+        <v>0.4189427342020401</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3196156790228142</v>
+        <v>0.3215156790228142</v>
       </c>
       <c r="C99">
-        <v>-200.8130745819186</v>
+        <v>-206.6934995146818</v>
       </c>
       <c r="D99">
-        <v>203.6559254180814</v>
+        <v>202.2525004853182</v>
       </c>
       <c r="E99">
-        <v>256.469</v>
+        <v>260.946</v>
       </c>
       <c r="F99">
-        <v>434.269</v>
+        <v>438.746</v>
       </c>
       <c r="G99">
         <v>29.8</v>
@@ -9399,37 +9399,37 @@
         <v>42.9</v>
       </c>
       <c r="M99">
-        <v>102.4006302</v>
+        <v>103.4563068</v>
       </c>
       <c r="N99">
-        <v>-59.50063020000001</v>
+        <v>-60.55630679999999</v>
       </c>
       <c r="O99">
-        <v>-8.925094530000001</v>
+        <v>-9.083446019999998</v>
       </c>
       <c r="P99">
-        <v>-50.57553567000001</v>
+        <v>-51.47286078</v>
       </c>
       <c r="Q99">
-        <v>-33.47553567000001</v>
+        <v>-34.37286078</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.508771446542616</v>
+        <v>5.240257169813924</v>
       </c>
       <c r="T99">
-        <v>21.17910228001896</v>
+        <v>31.76865342002844</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.062841410130306</v>
+        <v>0.06220017125142534</v>
       </c>
       <c r="W99">
-        <v>0.2209819954912739</v>
+        <v>0.2211331996189139</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4189427342020401</v>
+        <v>0.4146678083428357</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3215156790228142</v>
+        <v>0.3234156790228142</v>
       </c>
       <c r="C100">
-        <v>-206.6934995146818</v>
+        <v>-212.5547143842264</v>
       </c>
       <c r="D100">
-        <v>202.2525004853182</v>
+        <v>200.8682856157736</v>
       </c>
       <c r="E100">
-        <v>260.946</v>
+        <v>265.423</v>
       </c>
       <c r="F100">
-        <v>438.746</v>
+        <v>443.223</v>
       </c>
       <c r="G100">
         <v>29.8</v>
@@ -9481,37 +9481,37 @@
         <v>42.9</v>
       </c>
       <c r="M100">
-        <v>103.4563068</v>
+        <v>104.5119834</v>
       </c>
       <c r="N100">
-        <v>-60.55630679999999</v>
+        <v>-61.61198340000001</v>
       </c>
       <c r="O100">
-        <v>-9.083446019999998</v>
+        <v>-9.241797510000001</v>
       </c>
       <c r="P100">
-        <v>-51.47286078</v>
+        <v>-52.37018589</v>
       </c>
       <c r="Q100">
-        <v>-34.37286078</v>
+        <v>-35.27018589</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.240257169813924</v>
+        <v>10.43471433962785</v>
       </c>
       <c r="T100">
-        <v>31.76865342002844</v>
+        <v>63.53730684005688</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06220017125142534</v>
+        <v>0.06157188669333013</v>
       </c>
       <c r="W100">
-        <v>0.2211331996189139</v>
+        <v>0.2212813491177128</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4146678083428357</v>
+        <v>0.4104792446222009</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3234156790228142</v>
-      </c>
-      <c r="C101">
-        <v>-212.5547143842264</v>
-      </c>
-      <c r="D101">
-        <v>200.8682856157736</v>
-      </c>
-      <c r="E101">
-        <v>265.423</v>
-      </c>
-      <c r="F101">
-        <v>443.223</v>
-      </c>
-      <c r="G101">
-        <v>29.8</v>
-      </c>
-      <c r="H101">
-        <v>269.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>60</v>
-      </c>
-      <c r="K101">
-        <v>17.1</v>
-      </c>
-      <c r="L101">
-        <v>42.9</v>
-      </c>
-      <c r="M101">
-        <v>104.5119834</v>
-      </c>
-      <c r="N101">
-        <v>-61.61198340000001</v>
-      </c>
-      <c r="O101">
-        <v>-9.241797510000001</v>
-      </c>
-      <c r="P101">
-        <v>-52.37018589</v>
-      </c>
-      <c r="Q101">
-        <v>-35.27018589</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.43471433962785</v>
-      </c>
-      <c r="T101">
-        <v>63.53730684005688</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06157188669333013</v>
-      </c>
-      <c r="W101">
-        <v>0.2212813491177128</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4104792446222009</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
